--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,25 +647,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>59.3</v>
+        <v>53.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44.4</v>
+        <v>41.2</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,21 +674,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>66.7</v>
+        <v>59.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>52.4</v>
+        <v>40.9</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,48 +708,48 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>57.6</v>
+        <v>52.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N4" s="3" t="n">
-        <v>42.9</v>
+        <v>48.4</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,48 +830,48 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>U-U-N-D</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>U-U-N-N</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N6" s="3" t="n">
-        <v>56.5</v>
+        <v>46.2</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61.1</v>
+        <v>50.8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>47.2</v>
+        <v>42.4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>60</v>
+        <v>42.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57.1</v>
+        <v>60.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>41.7</v>
+        <v>36.5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>77.8</v>
+        <v>70</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>68</v>
+        <v>59.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>36</v>
+        <v>43.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1146,14 +1146,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44.9</v>
+        <v>46.8</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>52</v>
+        <v>63.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,48 +1196,48 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>40.9</v>
+        <v>45.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>50</v>
+        <v>41.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>37.5</v>
+        <v>54.8</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,25 +1379,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.9</v>
+        <v>54.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>43.1</v>
+        <v>47.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>66.7</v>
+        <v>46.4</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>57.1</v>
+        <v>57.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>42.9</v>
+        <v>41.5</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>70.7</v>
+        <v>63.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.7</v>
+        <v>43.1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>69.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>47.1</v>
+        <v>58.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1634,37 +1634,37 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>52</v>
+        <v>44.1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46.8</v>
+        <v>58.3</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>61.2</v>
+        <v>60.5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>60.7</v>
+        <v>53.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>44.6</v>
+        <v>41.5</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,25 +1928,25 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>59.5</v>
+        <v>66.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>42.9</v>
+        <v>37.7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>45</v>
+        <v>41.7</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>59.6</v>
+        <v>51.2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45.8</v>
+        <v>38.8</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>68.3</v>
+        <v>61.3</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>55</v>
+        <v>41.9</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>70.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>47.7</v>
+        <v>41</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>83.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>45.8</v>
+        <v>41.2</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>63.1</v>
+        <v>60</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2549,14 +2549,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45.2</v>
+        <v>40</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>66.7</v>
+        <v>68</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>51.5</v>
+        <v>40</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>58.3</v>
+        <v>61.3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2671,37 +2671,37 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="O36" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>60.6</v>
+        <v>59.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,14 +2854,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>43.7</v>
+        <v>37.3</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,25 +2904,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>45.5</v>
+        <v>43.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -2956,57 +2956,57 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
         <v>50</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,48 +3026,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>41.7</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>81.5</v>
+        <v>73.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3098,14 +3098,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.4</v>
+        <v>44.7</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>55.6</v>
+        <v>73.5</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>55.6</v>
+        <v>47.1</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,48 +3148,48 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,25 +3270,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>58.1</v>
+        <v>59.4</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>44.6</v>
+        <v>46.9</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>62.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>53.1</v>
+        <v>46.4</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>50.6</v>
+        <v>56.9</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -3342,14 +3342,14 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>44.6</v>
+        <v>41.2</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>47.2</v>
+        <v>50</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>50</v>
+        <v>43.1</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>63.3</v>
+        <v>52.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3464,14 +3464,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>44.3</v>
+        <v>40.6</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>58.8</v>
+        <v>57.1</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>44.1</v>
+        <v>42.9</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>66.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>39.7</v>
+        <v>42.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>62.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>51.7</v>
+        <v>42.6</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3586,14 +3586,14 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>41.7</v>
+        <v>44.9</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>52.6</v>
+        <v>49.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3708,26 +3708,26 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>47.4</v>
+        <v>50.9</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>57.1</v>
+        <v>48.1</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,48 +3819,48 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>56.7</v>
+        <v>75</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,25 +3941,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>40</v>
+        <v>45.8</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>65</v>
+        <v>72.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>45</v>
+        <v>55.6</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>46.4</v>
+        <v>43.1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>69.2</v>
+        <v>43.3</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>61.5</v>
+        <v>43.3</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>69</v>
+        <v>60.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>38.1</v>
+        <v>46.6</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4135,14 +4135,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>44</v>
+        <v>41.7</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>73.3</v>
+        <v>53.1</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46.7</v>
+        <v>43</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>76.2</v>
+        <v>53.1</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>42.9</v>
+        <v>42.2</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4307,25 +4307,25 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>46.2</v>
+        <v>53.8</v>
       </c>
       <c r="H63" s="4" t="n">
         <v>13</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4334,21 +4334,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,25 +4429,25 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>68.7</v>
+        <v>61.5</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46.3</v>
+        <v>44.1</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,21 +4456,21 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>66.7</v>
+        <v>56.4</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66">
@@ -4542,19 +4542,19 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>72.2</v>
+        <v>75</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4565,34 +4565,34 @@
         <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4612,48 +4612,48 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E68" s="4" t="n">
-        <v>45</v>
-      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-D</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="L68" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="N68" s="3" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,25 +4734,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>37.3</v>
+        <v>43.4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,21 +4761,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>35.7</v>
+        <v>53.3</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,48 +4795,48 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="E71" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="L71" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="H71" s="4" t="n">
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="O71" s="4" t="n">
         <v>36</v>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="72">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>72.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>54.5</v>
+        <v>34.9</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>61.1</v>
+        <v>66.7</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.1</v>
+        <v>55.3</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -5233,26 +5233,26 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>43.8</v>
+        <v>42</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>44</v>
+        <v>56.6</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>48</v>
+        <v>44.7</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>59.4</v>
+        <v>63.3</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>41.9</v>
+        <v>49.4</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>66</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>44</v>
+        <v>57.1</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,48 +5405,48 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>59.3</v>
+        <v>59</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-D</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G81" s="3" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="H81" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N81" s="3" t="n">
-        <v>57.1</v>
+        <v>44</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5710,37 +5710,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>52.4</v>
+        <v>70.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>47.6</v>
+        <v>43.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>47.5</v>
+        <v>64.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>37.5</v>
+        <v>41.2</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>69.2</v>
+        <v>58.1</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>44.6</v>
+        <v>41.9</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>42.9</v>
+        <v>45.9</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5832,48 +5832,48 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>58.3</v>
+        <v>57.6</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="G88" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N88" s="3" t="n">
-        <v>52.2</v>
+        <v>42.9</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>49.3</v>
+        <v>45.3</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,26 +5904,26 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>43.5</v>
+        <v>48</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,25 +5954,25 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>56.5</v>
+        <v>50.9</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>41.9</v>
+        <v>43.9</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>63</v>
+        <v>51.4</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>40.7</v>
+        <v>43.2</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,37 +6015,37 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>51</v>
+        <v>40.8</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>42</v>
+        <v>47.7</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>52.5</v>
+        <v>43.6</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>42.4</v>
+        <v>47.3</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,25 +6137,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>38.1</v>
+        <v>40.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>44.4</v>
+        <v>52.8</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6392,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.8</v>
+        <v>43.6</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,10 +6408,10 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>58.6</v>
+        <v>48.9</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>44.8</v>
+        <v>42.2</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>57.1</v>
+        <v>52.7</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>40.5</v>
+        <v>40.2</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,21 +6530,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>48.3</v>
+        <v>53</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>41.7</v>
+        <v>36.4</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>44.7</v>
+        <v>55.5</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>46</v>
+        <v>48.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>47.8</v>
+        <v>53.3</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6625,25 +6625,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>62.2</v>
+        <v>45.1</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>60.9</v>
+        <v>58.8</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -6819,14 +6819,14 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>40.2</v>
+        <v>41.2</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>48</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>36</v>
+        <v>57.1</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,25 +6869,25 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>74.3</v>
+        <v>49.3</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>40</v>
+        <v>46.4</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,21 +6896,21 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
-        <v>80</v>
+        <v>46.7</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7176,25 +7176,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>58.8</v>
+        <v>51.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q3" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -7238,19 +7238,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45</v>
+        <v>54.8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7258,37 +7258,37 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>40</v>
+        <v>41.9</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7389,48 +7389,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>83.3</v>
+        <v>53.8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>38.9</v>
+        <v>69.2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,45 +7460,45 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>62.5</v>
+        <v>69.2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>2</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7602,25 +7602,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>54.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7632,18 +7632,18 @@
         <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,25 +7673,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>54.5</v>
+        <v>64</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7755,37 +7755,37 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -7806,46 +7806,46 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -8019,46 +8019,46 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="N15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8099,25 +8099,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>52.6</v>
+        <v>75</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>36.8</v>
+        <v>46.4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8126,21 +8126,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>64.7</v>
+        <v>60</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -8252,14 +8252,14 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>41.2</v>
+        <v>45</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8268,18 +8268,18 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>9</v>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8323,14 +8323,14 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8454,25 +8454,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>76.2</v>
+        <v>57.1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8481,18 +8481,18 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>7</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>7</v>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8667,37 +8667,37 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8809,10 +8809,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>64</v>
+        <v>57.1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -8820,14 +8820,14 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>64</v>
+        <v>38.1</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>72.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9235,25 +9235,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9262,21 +9262,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -9368,46 +9368,46 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-N</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-U</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="M34" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>60</v>
+        <v>69.2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -9530,37 +9530,37 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -9723,39 +9723,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>58.8</v>
+        <v>43.8</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9803,44 +9803,48 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-D</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -9861,39 +9865,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
@@ -9904,7 +9908,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
@@ -9932,53 +9936,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q42" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -9999,7 +10007,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10008,10 +10016,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>57.1</v>
+        <v>72.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -10019,37 +10027,37 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
         <v>75</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -10070,7 +10078,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10079,10 +10087,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -10090,33 +10098,37 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -10208,7 +10220,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10217,48 +10229,48 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>14</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -10279,7 +10291,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10288,48 +10300,48 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>48.3</v>
+        <v>62.9</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>51.7</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>41.7</v>
+        <v>53.3</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -10421,57 +10433,57 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>60</v>
+        <v>41.2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46.7</v>
+        <v>35.3</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -10492,7 +10504,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10501,10 +10513,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>52.9</v>
+        <v>69.2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10512,14 +10524,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>52.9</v>
+        <v>57.7</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10528,10 +10540,10 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -10539,10 +10551,10 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -10563,7 +10575,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10572,44 +10584,48 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="G51" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N51" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="n">
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="Q51" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr"/>
-      <c r="Q51" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10701,7 +10717,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10710,25 +10726,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>85.7</v>
+        <v>58.3</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10737,21 +10753,21 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -10843,19 +10859,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10866,30 +10882,34 @@
         <v>50</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-U</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -10981,7 +11001,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10990,48 +11010,48 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G57" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q57" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -11052,7 +11072,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11061,48 +11081,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -11123,7 +11143,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11132,25 +11152,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>83.3</v>
+        <v>43.8</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11159,21 +11179,21 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -11194,7 +11214,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11203,37 +11223,37 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>66.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>33.3</v>
+        <v>46.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -11241,10 +11261,10 @@
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -11336,7 +11356,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11345,10 +11365,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11356,26 +11376,26 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>54.5</v>
+        <v>51.9</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -11383,10 +11403,10 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -11407,7 +11427,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11416,25 +11436,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -11446,18 +11466,18 @@
         <v>100</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P63" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -11549,7 +11569,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11558,25 +11578,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>58.3</v>
+        <v>63.9</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11585,21 +11605,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>80</v>
+        <v>68.8</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -11691,7 +11711,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11714,7 +11734,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11754,7 +11774,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11763,10 +11783,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -11774,26 +11794,26 @@
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -11804,7 +11824,7 @@
         <v>66.7</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
@@ -11896,7 +11916,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11905,10 +11925,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>63.6</v>
+        <v>64.7</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11916,26 +11936,26 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>54.5</v>
+        <v>47.1</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -11943,10 +11963,10 @@
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -11967,53 +11987,57 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="inlineStr"/>
       <c r="Q71" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
@@ -12318,7 +12342,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12327,10 +12351,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -12341,16 +12365,16 @@
         <v>50</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M76" s="3" t="n">
@@ -12361,7 +12385,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
@@ -12460,57 +12484,57 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -12531,7 +12555,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12540,25 +12564,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>57.1</v>
+        <v>61.1</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12567,21 +12591,21 @@
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>33.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -12673,57 +12697,57 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>47.8</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -13028,7 +13052,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -13037,10 +13061,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>57.1</v>
+        <v>90</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -13051,11 +13075,11 @@
         <v>50</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -13064,10 +13088,10 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -13075,10 +13099,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -13099,7 +13123,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13108,37 +13132,37 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>66.7</v>
+        <v>67.7</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>66.7</v>
+        <v>45.2</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13146,10 +13170,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -13170,19 +13194,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>50</v>
+        <v>57.6</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -13190,37 +13214,37 @@
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>50</v>
+        <v>57.6</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -13241,7 +13265,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -13250,10 +13274,10 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>53.8</v>
+        <v>52.9</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -13261,37 +13285,37 @@
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>46.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90">
@@ -13312,19 +13336,19 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>44.4</v>
+        <v>52.4</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13332,14 +13356,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13348,10 +13372,10 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -13359,10 +13383,10 @@
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
@@ -13383,7 +13407,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13392,48 +13416,48 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>56</v>
+        <v>46.7</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I91" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="P91" s="3" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
@@ -13525,7 +13549,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13534,10 +13558,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>87.5</v>
+        <v>54.2</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -13545,14 +13569,14 @@
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13561,21 +13585,21 @@
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -13809,7 +13833,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13818,37 +13842,37 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>37.5</v>
+        <v>43.8</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -13856,10 +13880,10 @@
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -13951,7 +13975,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13960,10 +13984,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>46.2</v>
+        <v>45.2</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13971,23 +13995,23 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>46.2</v>
+        <v>48.4</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="N99" s="4" t="n">
         <v>11</v>
@@ -13998,7 +14022,7 @@
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>63.6</v>
+        <v>45.5</v>
       </c>
       <c r="Q99" s="4" t="n">
         <v>11</v>
@@ -14022,7 +14046,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14031,25 +14055,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>46.7</v>
+        <v>57.7</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>63.3</v>
+        <v>50</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14058,21 +14082,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -14093,7 +14117,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14102,48 +14126,48 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J101" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I101" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J101" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-U</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N101" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P101" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -14306,7 +14330,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14315,25 +14339,25 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>68.8</v>
+        <v>62.5</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -14342,21 +14366,21 @@
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -14377,57 +14401,57 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>83.3</v>
+        <v>47.8</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I105" s="3" t="n">
-        <v>58.3</v>
+        <v>60.9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>80</v>
+        <v>46.2</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,48 +586,48 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-D</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N2" s="3" t="n">
-        <v>39.1</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>37</v>
+        <v>37.7</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>35.7</v>
+        <v>41.7</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,48 +1074,48 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>59.2</v>
+        <v>68</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-N</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>N-N-D-U</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N10" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46.8</v>
+        <v>51.7</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>63.5</v>
+        <v>61.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>50.8</v>
+        <v>47.3</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,25 +1318,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>38.1</v>
+        <v>39.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>64.3</v>
+        <v>51.8</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.3</v>
+        <v>42.9</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>55.6</v>
+        <v>40.7</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,48 +1623,48 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>58.8</v>
+        <v>45.7</v>
       </c>
       <c r="E19" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="H19" s="4" t="n">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>34</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.5</v>
+        <v>59.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>38.9</v>
+        <v>45.1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>79.2</v>
+        <v>61.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1748,7 +1748,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1756,14 +1756,14 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40.7</v>
+        <v>36.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
         <v>53.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>41.5</v>
+        <v>40.7</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1797,57 +1797,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>55.6</v>
+        <v>48.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>40</v>
+        <v>41.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>87.5</v>
+        <v>70.3</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>75</v>
+        <v>43.2</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -2102,57 +2102,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>44.4</v>
+        <v>56.5</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>51.9</v>
+        <v>47.8</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>38.5</v>
+        <v>54.5</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>61.5</v>
+        <v>72.7</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,25 +2172,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>69.5</v>
+        <v>53.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>42.4</v>
+        <v>49</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>60</v>
+        <v>52.7</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2305,14 +2305,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46.9</v>
+        <v>48.5</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>56.2</v>
+        <v>61.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>40.6</v>
+        <v>45.7</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>85.7</v>
+        <v>81.2</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.9</v>
+        <v>56.2</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>41</v>
+        <v>47.7</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>41.2</v>
+        <v>45.8</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>43.5</v>
+        <v>46.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>63.6</v>
+        <v>59.1</v>
       </c>
       <c r="L33" s="4" t="n">
         <v>22</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>45.5</v>
+        <v>36.4</v>
       </c>
       <c r="O33" s="4" t="n">
         <v>22</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2549,14 +2549,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>40</v>
+        <v>51.2</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>64.2</v>
+        <v>60.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>44.4</v>
+        <v>43.9</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>73.5</v>
+        <v>51.2</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>59.3</v>
+        <v>63.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,14 +2854,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>37.3</v>
+        <v>58.3</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="L39" s="4" t="n">
         <v>20</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>20</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,25 +3087,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>73.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>73.5</v>
+        <v>59.1</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>58.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>43.5</v>
+        <v>39.9</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55.6</v>
+        <v>68.8</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>41.7</v>
+        <v>45.3</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,25 +3636,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>59.3</v>
+        <v>69.8</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>40.7</v>
+        <v>34</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>57.1</v>
+        <v>69.2</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46.4</v>
+        <v>38.5</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3758,25 +3758,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>45.2</v>
+        <v>51.9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>48.1</v>
+        <v>44.4</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3785,21 +3785,21 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>43.6</v>
+        <v>49.2</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>47.3</v>
+        <v>49.2</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,48 +3819,48 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>N-N-N-D</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>N-N-N-N</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
       <c r="N55" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,25 +3941,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>45.8</v>
+        <v>40</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3968,21 +3968,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>72.2</v>
+        <v>65</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>55.6</v>
+        <v>45</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>58.6</v>
+        <v>64.7</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4684,14 +4684,14 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>52.9</v>
+        <v>58.8</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>52.8</v>
+        <v>63.6</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>51.9</v>
+        <v>44.4</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4989,14 +4989,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>56.2</v>
+        <v>42</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>52.1</v>
+        <v>40.6</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5039,48 +5039,48 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>72.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-N</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G75" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-D</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="n">
+      <c r="N75" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="L75" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="n">
-        <v>33.3</v>
-      </c>
       <c r="O75" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>34.9</v>
+        <v>40</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>63.3</v>
+        <v>58.5</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>49.4</v>
+        <v>47.2</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>57.1</v>
+        <v>37</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>54.1</v>
+        <v>43.1</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>45.9</v>
+        <v>49.2</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>48.4</v>
+        <v>65.3</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>53.1</v>
+        <v>41.1</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>60.9</v>
+        <v>74</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>52.2</v>
+        <v>42</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -6209,14 +6209,14 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>41.1</v>
+        <v>37.8</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>77.8</v>
+        <v>81.8</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>37</v>
+        <v>45.5</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>54.2</v>
+        <v>56.6</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -6331,14 +6331,14 @@
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>57.1</v>
+        <v>58.7</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>66.7</v>
+        <v>56.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,14 +6697,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>41.7</v>
+        <v>45</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>73.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>39.1</v>
+        <v>52</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6808,25 +6808,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>58.8</v>
+        <v>59.7</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="O104" s="4" t="n">
         <v>14</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7105,25 +7105,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>57.1</v>
+        <v>81.2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>42.9</v>
+        <v>43.8</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7318,48 +7318,44 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>33.3</v>
+        <v>53.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7664,7 +7660,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,25 +7669,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7700,21 +7696,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -7735,7 +7731,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7744,48 +7740,48 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>64</v>
+        <v>57.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>40</v>
+        <v>57.9</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -7948,7 +7944,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,25 +7953,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7984,21 +7980,21 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -8161,19 +8157,19 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>69.2</v>
+        <v>57.1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8181,37 +8177,37 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>33.3</v>
+        <v>80</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -8303,46 +8299,46 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N19" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8350,10 +8346,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -8374,7 +8370,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,10 +8379,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8394,26 +8390,26 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N20" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -8421,10 +8417,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -8445,7 +8441,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8454,48 +8450,48 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="G21" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="N21" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="Q21" s="4" t="n">
         <v>14</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -8516,57 +8512,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>47.1</v>
+        <v>83.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8725,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8738,25 +8734,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8765,21 +8761,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -8871,19 +8867,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -8891,14 +8887,14 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -8907,21 +8903,21 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -8942,19 +8938,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>66.7</v>
+        <v>51.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8962,14 +8958,14 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>41.7</v>
+        <v>63.6</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -8978,10 +8974,10 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -8989,10 +8985,10 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -9084,7 +9080,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9093,10 +9089,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>63.6</v>
+        <v>47.2</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -9104,14 +9100,14 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>40.9</v>
+        <v>58.3</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -9120,21 +9116,21 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>60</v>
+        <v>69.2</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -9155,7 +9151,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9164,48 +9160,44 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -9226,7 +9218,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9235,48 +9227,48 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-D</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="n">
         <v>83.3</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -9297,7 +9289,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9306,37 +9298,37 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>81.2</v>
+        <v>76.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>56.2</v>
+        <v>41.2</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -9344,10 +9336,10 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -9368,57 +9360,57 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-D</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -9652,7 +9644,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9661,10 +9653,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -9672,26 +9664,26 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>55</v>
+        <v>40.6</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -9699,10 +9691,10 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -9723,7 +9715,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9732,25 +9724,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>56.2</v>
+        <v>75</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>43.8</v>
+        <v>68.8</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9759,10 +9751,10 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -9770,10 +9762,10 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>42.9</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -10007,7 +9999,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10016,25 +10008,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>72.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>44.4</v>
+        <v>52.9</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -10043,21 +10035,21 @@
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>75</v>
+        <v>57.1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -10362,7 +10354,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10371,25 +10363,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>63.6</v>
+        <v>59.5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>63.6</v>
+        <v>40.5</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10398,21 +10390,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -10646,7 +10638,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10655,48 +10647,48 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>43.8</v>
+        <v>64.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -10788,19 +10780,19 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -10808,14 +10800,14 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>59.5</v>
+        <v>50</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -10824,21 +10816,21 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="n">
         <v>62.5</v>
       </c>
-      <c r="N54" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n">
-        <v>43.8</v>
-      </c>
       <c r="Q54" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -10859,57 +10851,57 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -11001,7 +10993,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -11010,48 +11002,48 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -11845,57 +11837,57 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M69" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -12200,7 +12192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12209,25 +12201,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>42.3</v>
+        <v>45.5</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12247,7 +12239,7 @@
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>47.1</v>
+        <v>52.9</v>
       </c>
       <c r="Q74" s="4" t="n">
         <v>17</v>
@@ -12271,7 +12263,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12280,30 +12272,30 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M75" s="3" t="n">
@@ -12314,7 +12306,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P75" s="3" t="n">
@@ -12342,7 +12334,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12351,14 +12343,14 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
@@ -12369,12 +12361,12 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M76" s="3" t="n">
@@ -12555,7 +12547,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12564,48 +12556,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>61.1</v>
+        <v>52.2</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I79" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M79" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -13123,7 +13115,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13132,10 +13124,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>67.7</v>
+        <v>44.8</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -13143,37 +13135,37 @@
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>45.2</v>
+        <v>51.7</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>63.6</v>
+        <v>33.3</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>45.5</v>
+        <v>75</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -13478,19 +13470,19 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13498,14 +13490,14 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>63.6</v>
+        <v>45.8</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13514,21 +13506,21 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>66.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
@@ -13620,7 +13612,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13629,48 +13621,48 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>77.8</v>
+        <v>75</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M94" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N94" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N94" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q94" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -13762,7 +13754,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13771,10 +13763,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13782,14 +13774,14 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>44.4</v>
+        <v>61.9</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13809,7 +13801,7 @@
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="Q96" s="4" t="n">
         <v>7</v>
@@ -14188,7 +14180,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14197,25 +14189,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>41.7</v>
+        <v>54.5</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14224,21 +14216,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>60</v>
+        <v>77.8</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -14259,7 +14251,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14268,25 +14260,25 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>38.5</v>
+        <v>47.4</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -14295,21 +14287,21 @@
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -14330,7 +14322,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14339,48 +14331,48 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>62.5</v>
+        <v>53.8</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,48 +708,48 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>52.2</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>67</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.5</v>
+        <v>57.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>39.2</v>
+        <v>45.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>70</v>
+        <v>61.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>65.7</v>
+        <v>59.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,37 +902,37 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45.7</v>
+        <v>42.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>72.7</v>
+        <v>73.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -963,14 +963,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>54.5</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>7</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66.3</v>
+        <v>71.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>41.9</v>
+        <v>35.8</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>61.1</v>
+        <v>64.3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>44.4</v>
+        <v>35.7</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>59.2</v>
+        <v>62</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44.9</v>
+        <v>51.2</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>64.7</v>
+        <v>63.4</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>47.1</v>
+        <v>53.7</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>54.5</v>
+        <v>64.3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>48.5</v>
+        <v>53.6</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>60</v>
+        <v>73.3</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>15</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>15</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>43.8</v>
+        <v>41</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>77.3</v>
+        <v>57.1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.9</v>
+        <v>49.4</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>38.9</v>
+        <v>45.5</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>68.5</v>
+        <v>75.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45.4</v>
+        <v>37</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>71.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>60.5</v>
+        <v>61.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>53.7</v>
+        <v>60.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>60.9</v>
+        <v>62.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1939,14 +1939,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44.9</v>
+        <v>43.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46.2</v>
+        <v>42.1</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>85.7</v>
+        <v>48.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>42.9</v>
+        <v>51.5</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,25 +2172,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>69.5</v>
+        <v>54</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>42.4</v>
+        <v>48.7</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>60</v>
+        <v>53.6</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>50</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2305,14 +2305,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46.2</v>
+        <v>45.6</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>51.9</v>
+        <v>48.3</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>40.7</v>
+        <v>40</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>73</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2427,14 +2427,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>40.5</v>
+        <v>45.7</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>57.9</v>
+        <v>74.2</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>52.6</v>
+        <v>48.4</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>81.2</v>
+        <v>75.8</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45.8</v>
+        <v>40.9</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>55.6</v>
+        <v>50.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,14 +2610,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>48.1</v>
+        <v>45.2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>62.5</v>
+        <v>46.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>60.7</v>
+        <v>55.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2793,14 +2793,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>43.6</v>
+        <v>41.7</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>52.3</v>
+        <v>54.1</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>50</v>
+        <v>45.9</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>70.8</v>
+        <v>66.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2915,37 +2915,37 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>58.3</v>
+        <v>41.7</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>100</v>
+        <v>36.4</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,45 +3026,45 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>47.8</v>
+        <v>75</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>43.5</v>
+        <v>41.7</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>6</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
         <v>6</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>64.8</v>
+        <v>58.8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3098,14 +3098,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>52.4</v>
+        <v>64.7</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>78.8</v>
+        <v>58.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,25 +3270,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>51.6</v>
+        <v>59.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>44.7</v>
+        <v>36.6</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>40.9</v>
+        <v>50</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>56.1</v>
+        <v>54.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40.8</v>
+        <v>48.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>48.6</v>
+        <v>45.5</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3517,22 +3517,22 @@
         <v>66.2</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>41.9</v>
+        <v>39.7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>58.5</v>
+        <v>64</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>41.5</v>
+        <v>40</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>38.8</v>
+        <v>40.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>77.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>38.9</v>
+        <v>35.3</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3708,26 +3708,26 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>47.4</v>
+        <v>51.8</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,48 +4002,48 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="E58" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="H58" s="4" t="n">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="O58" s="4" t="n">
         <v>28</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,10 +4063,10 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -4074,14 +4074,14 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>41.9</v>
+        <v>34.7</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>64.7</v>
+        <v>68.3</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>52.9</v>
+        <v>39</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>70.5</v>
+        <v>63.9</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>43.2</v>
+        <v>41.7</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>47.4</v>
+        <v>42.4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,25 +4185,25 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>72.7</v>
+        <v>61.4</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>63.6</v>
+        <v>47.7</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>68.7</v>
+        <v>65.8</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46.3</v>
+        <v>45.2</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>66.7</v>
+        <v>63.5</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>70.3</v>
+        <v>59.1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>37.5</v>
+        <v>42.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>68.2</v>
+        <v>57.7</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>36.4</v>
+        <v>46.2</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4745,14 +4745,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>45.8</v>
+        <v>38.4</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,21 +4761,21 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>72.2</v>
+        <v>62.1</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>47.2</v>
+        <v>48.3</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>75</v>
+        <v>60.3</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>43.2</v>
+        <v>45.6</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>80</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>50</v>
+        <v>35.7</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>70.8</v>
+        <v>60.8</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>45.8</v>
+        <v>51</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,25 +5222,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.1</v>
+        <v>52.9</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>53.1</v>
+        <v>45.6</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5416,14 +5416,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>70</v>
+        <v>68.2</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>36</v>
+        <v>59.1</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>59.1</v>
+        <v>61.8</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5782,14 +5782,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>42.4</v>
+        <v>41.9</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>66.7</v>
+        <v>52.3</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5832,25 +5832,25 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>43.3</v>
+        <v>41.2</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>56.5</v>
+        <v>62.5</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>52.2</v>
+        <v>46.9</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,37 +6015,37 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>43.1</v>
+        <v>42</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>39.1</v>
+        <v>51.6</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>52.2</v>
+        <v>48.4</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6198,25 +6198,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>73</v>
+        <v>84.7</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>44.4</v>
+        <v>39</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>35.3</v>
+        <v>46.2</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,25 +6320,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>54.2</v>
+        <v>47</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>44.4</v>
+        <v>39</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>72</v>
+        <v>164</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>57.1</v>
+        <v>47.1</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.9</v>
+        <v>42.6</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6392,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>58.6</v>
+        <v>53.4</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
         <v>44.8</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>66.7</v>
+        <v>56.8</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,37 +6697,37 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>47.4</v>
+        <v>40</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -6799,19 +6799,19 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -6819,14 +6819,14 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>46.3</v>
+        <v>42.9</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>77.3</v>
+        <v>52.6</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>40.9</v>
+        <v>52.6</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7247,25 +7247,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>44.4</v>
+        <v>53.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>83.3</v>
+        <v>63.6</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7318,48 +7318,48 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7471,37 +7471,37 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>60</v>
+        <v>61.1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -7522,49 +7522,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7656,7 +7664,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7665,25 +7673,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46.2</v>
+        <v>36.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7692,21 +7700,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7727,7 +7735,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7736,25 +7744,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>80</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>40</v>
+        <v>51.7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7766,18 +7774,18 @@
         <v>100</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -7869,7 +7877,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7878,10 +7886,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7889,23 +7897,23 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>4</v>
@@ -8082,7 +8090,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8091,48 +8099,48 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>43.8</v>
+        <v>59.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>43.8</v>
+        <v>40.6</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -8153,57 +8161,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>85.7</v>
+        <v>41.7</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8366,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8375,10 +8383,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>58.6</v>
+        <v>81.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8386,14 +8394,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8402,21 +8410,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -8437,7 +8445,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8446,48 +8454,48 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>57.1</v>
+        <v>65</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>57.1</v>
+        <v>42.5</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>57.1</v>
+        <v>57.9</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -8650,34 +8658,34 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>81.2</v>
+        <v>40</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>43.8</v>
+        <v>70</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -8686,21 +8694,21 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -8721,7 +8729,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8730,25 +8738,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>84.2</v>
+        <v>56.1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>52.6</v>
+        <v>41.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8757,21 +8765,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -8934,7 +8942,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8943,48 +8951,48 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>56.2</v>
+        <v>58.6</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>43.8</v>
+        <v>55.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -9076,19 +9084,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -9096,37 +9104,37 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -9214,7 +9222,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9223,10 +9231,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>68.8</v>
+        <v>66.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9234,37 +9242,37 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>43.8</v>
+        <v>48.5</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q32" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -9285,7 +9293,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9294,25 +9302,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>100</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9321,10 +9329,10 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -9332,10 +9340,10 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -9427,7 +9435,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9436,44 +9444,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>75</v>
+        <v>54.2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>55.6</v>
+      </c>
       <c r="N35" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q35" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -9636,7 +9648,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9645,25 +9657,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55.9</v>
+        <v>64.7</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>34</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>58.8</v>
+        <v>47.1</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9672,21 +9684,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>54.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>72.7</v>
+        <v>69.2</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
@@ -9778,53 +9790,57 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q40" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -9916,57 +9932,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -9987,19 +10003,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>64.7</v>
+        <v>40</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -10007,26 +10023,26 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -10034,10 +10050,10 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -10200,7 +10216,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10209,25 +10225,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>37.5</v>
+        <v>45.5</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10243,11 +10259,11 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q46" s="4" t="n">
         <v>2</v>
@@ -10271,7 +10287,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10280,25 +10296,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>62.5</v>
+        <v>58.1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>54.2</v>
+        <v>51.6</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10307,21 +10323,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -10484,7 +10500,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10493,10 +10509,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>64</v>
+        <v>61.1</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10504,14 +10520,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10520,21 +10536,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -10626,7 +10642,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10635,25 +10651,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10662,21 +10678,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -10697,46 +10713,46 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -10747,7 +10763,7 @@
         <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -11052,7 +11068,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11061,37 +11077,37 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>69.2</v>
+        <v>57.9</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>53.8</v>
+        <v>47.4</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11115,10 @@
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -11123,7 +11139,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11132,25 +11148,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
         <v>40</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11159,21 +11175,21 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -11194,7 +11210,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11203,25 +11219,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>55</v>
+        <v>62.9</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>60</v>
+        <v>45.7</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11230,21 +11246,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -11265,7 +11281,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11274,48 +11290,48 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>77.8</v>
+        <v>45.5</v>
       </c>
       <c r="G61" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="N61" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J61" s="4" t="n">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Q61" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q61" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -11549,7 +11565,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11558,25 +11574,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>73.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>47.4</v>
+        <v>51.4</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11585,21 +11601,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>77.8</v>
+        <v>58.8</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>44.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
@@ -11620,7 +11636,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11629,25 +11645,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11667,7 +11683,7 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>4</v>
@@ -11896,7 +11912,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11905,25 +11921,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>75</v>
+        <v>52.9</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>56.2</v>
+        <v>35.3</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11932,14 +11948,14 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P70" s="3" t="n">
@@ -12322,7 +12338,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12331,25 +12347,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12358,21 +12374,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -12393,7 +12409,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12402,25 +12418,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12429,21 +12445,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>33.3</v>
+        <v>64.3</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
@@ -12464,7 +12480,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12473,10 +12489,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>64.7</v>
+        <v>54.8</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12484,37 +12500,37 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>58.8</v>
+        <v>42.9</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -12677,7 +12693,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12686,37 +12702,37 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12724,10 +12740,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -13103,7 +13119,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13112,25 +13128,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>62.5</v>
+        <v>41.7</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13139,10 +13155,10 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13150,10 +13166,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
@@ -13174,7 +13190,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13183,48 +13199,48 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>66.7</v>
+        <v>57.4</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="P88" s="3" t="n">
         <v>44.4</v>
       </c>
-      <c r="J88" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q88" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -13387,7 +13403,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13396,25 +13412,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>57.9</v>
+        <v>47.5</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>42.1</v>
+        <v>37.5</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13423,21 +13439,21 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -13600,7 +13616,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13609,10 +13625,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13620,14 +13636,14 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>46.7</v>
+        <v>70</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -13636,10 +13652,10 @@
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -13647,10 +13663,10 @@
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -13742,34 +13758,34 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13778,21 +13794,21 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -13813,7 +13829,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13822,48 +13838,48 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>64.7</v>
+        <v>58.1</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>52.9</v>
+        <v>48.4</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>42.9</v>
+        <v>61.5</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -14168,7 +14184,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14177,48 +14193,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -14310,34 +14326,34 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>72.7</v>
+        <v>38.9</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -14346,21 +14362,21 @@
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>57.4</v>
+        <v>74.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45.6</v>
+        <v>39.2</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>61.5</v>
+        <v>70</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>59.2</v>
+        <v>65.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,37 +902,37 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>42.3</v>
+        <v>45.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>71.7</v>
+        <v>69.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>35.8</v>
+        <v>40.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>64.3</v>
+        <v>72.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>35.7</v>
+        <v>50</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,25 +1196,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>76.7</v>
+        <v>48.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>46.7</v>
+        <v>58.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>66.7</v>
+        <v>56</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,48 +1318,48 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>U-U-D-D</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>U-U-D-U</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>69.5</v>
-      </c>
       <c r="L14" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>40.7</v>
+        <v>37.5</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>57.1</v>
+        <v>77.3</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>49.4</v>
+        <v>40.9</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>45.5</v>
+        <v>38.9</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>61.2</v>
+        <v>60.8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40.3</v>
+        <v>36.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>60.7</v>
+        <v>54.5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>44.6</v>
+        <v>40</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1817,37 +1817,37 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>51.7</v>
+        <v>45.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>81.5</v>
+        <v>50</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>51.9</v>
+        <v>41.7</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>55.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>43.5</v>
+        <v>38.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>48.5</v>
+        <v>85.7</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>51.5</v>
+        <v>42.9</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>78</v>
+        <v>88.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2244,14 +2244,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>76.3</v>
+        <v>86.7</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>62.7</v>
+        <v>46.7</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>85.7</v>
+        <v>78.8</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>7</v>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.7</v>
+        <v>55.6</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,14 +2610,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45.2</v>
+        <v>48.1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46.9</v>
+        <v>62.5</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>56.2</v>
+        <v>62.5</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,37 +2660,37 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>58.3</v>
+        <v>48.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="L36" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>55.8</v>
+        <v>64.2</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>54.1</v>
+        <v>73.5</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>45.9</v>
+        <v>50</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,48 +2843,48 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>64.5</v>
+        <v>42.6</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>41.9</v>
+        <v>46.3</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>53.8</v>
+        <v>47.1</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,45 +3026,45 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>75</v>
+        <v>47.8</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>41.7</v>
+        <v>43.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>6</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="O42" s="4" t="n">
         <v>6</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,25 +3087,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>58.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>64.7</v>
+        <v>38.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>58.3</v>
+        <v>69</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>58.3</v>
+        <v>41.4</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,25 +3148,25 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>89.5</v>
+        <v>70.2</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>52.6</v>
+        <v>44.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>58.3</v>
+        <v>55.6</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,25 +3270,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>59.2</v>
+        <v>51.6</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>36.6</v>
+        <v>44.7</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>50</v>
+        <v>40.9</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>54.7</v>
+        <v>54.3</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -3342,14 +3342,14 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48.7</v>
+        <v>46.3</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>63.6</v>
+        <v>49.2</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>45.5</v>
+        <v>49.2</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,25 +3392,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>58.1</v>
+        <v>59.8</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>43.5</v>
+        <v>48.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55.6</v>
+        <v>58.2</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3517,22 +3517,22 @@
         <v>66.2</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>39.7</v>
+        <v>41.9</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>64</v>
+        <v>58.5</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
       <c r="E51" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>44</v>
-      </c>
       <c r="H51" s="4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,25 +3636,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>40.7</v>
+        <v>39.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>35.3</v>
+        <v>38.9</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>48.6</v>
+        <v>63.2</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>45.9</v>
+        <v>40.8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,18 +3846,18 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>83.3</v>
+        <v>58.3</v>
       </c>
       <c r="L55" s="4" t="n">
         <v>12</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>58.3</v>
+        <v>33.3</v>
       </c>
       <c r="O55" s="4" t="n">
         <v>12</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.9</v>
+        <v>63.4</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>42.4</v>
+        <v>53.8</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,25 +4246,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>50.7</v>
+        <v>37.9</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>63.6</v>
+        <v>70.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>49.1</v>
+        <v>37.5</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,37 +4368,37 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>48.5</v>
+        <v>57.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45.5</v>
+        <v>39.3</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K64" s="3" t="n">
         <v>50</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4406,10 +4406,10 @@
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>65.8</v>
+        <v>68.7</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45.2</v>
+        <v>46.3</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>63.5</v>
+        <v>66.7</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>59.1</v>
+        <v>61</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>42.4</v>
+        <v>36.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>57.7</v>
+        <v>58.3</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46.2</v>
+        <v>41.7</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,48 +5222,48 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>52.9</v>
+        <v>52.1</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G78" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>187</v>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N78" s="3" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>63.3</v>
+        <v>58.9</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>49.4</v>
+        <v>46.7</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,18 +5310,18 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="L79" s="4" t="n">
         <v>28</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>57.1</v>
+        <v>35.7</v>
       </c>
       <c r="O79" s="4" t="n">
         <v>28</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>65.3</v>
+        <v>63.2</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5416,14 +5416,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>68.2</v>
+        <v>70</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>59.1</v>
+        <v>36</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>83.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>33.3</v>
+        <v>64.7</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5493,21 +5493,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5649,25 +5649,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>61.8</v>
+        <v>60.5</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>41.2</v>
+        <v>44.2</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>35.7</v>
+        <v>45</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5710,48 +5710,48 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>39</v>
+        <v>43.1</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5832,48 +5832,48 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>53.3</v>
+        <v>58.3</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G88" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>165</v>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N88" s="3" t="n">
-        <v>46.9</v>
+        <v>52.2</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>48.4</v>
+        <v>64.8</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>53.1</v>
+        <v>41.6</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>60.9</v>
+        <v>72.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>52.2</v>
+        <v>43.1</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6198,25 +6198,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>84.7</v>
+        <v>67.3</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>39</v>
+        <v>42.3</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,25 +6259,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>45.9</v>
+        <v>50</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>81.2</v>
+        <v>58.2</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>50</v>
+        <v>58.2</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,25 +6320,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>47</v>
+        <v>54.2</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>39</v>
+        <v>44.4</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>47.1</v>
+        <v>57.1</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>57.7</v>
+        <v>57.5</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6392,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>44.8</v>
+        <v>41.3</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,48 +6503,48 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>62.9</v>
+        <v>52.1</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G99" s="3" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="H99" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N99" s="3" t="n">
-        <v>46.3</v>
+        <v>45</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>39.3</v>
+        <v>42.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>66.7</v>
+        <v>56</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>40.7</v>
+        <v>42.7</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>62.1</v>
+        <v>45.5</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -6636,14 +6636,14 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>43.9</v>
+        <v>46.9</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>60.9</v>
+        <v>45.3</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>52.2</v>
+        <v>56.6</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>73.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>42.3</v>
+        <v>43.1</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>76.2</v>
+        <v>60</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>57.1</v>
+        <v>46.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7318,48 +7318,48 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-N</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-U</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M5" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7471,37 +7471,37 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>61.1</v>
+        <v>60</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,25 +7673,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>36.4</v>
+        <v>43.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7703,7 +7703,7 @@
         <v>66.7</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,48 +7815,48 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77.8</v>
+        <v>55.6</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7968,14 +7968,14 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>37.9</v>
+        <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7984,21 +7984,21 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>69.2</v>
+        <v>50</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8161,57 +8161,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-N</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-U</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P17" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8454,48 +8454,48 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>65</v>
+        <v>59.3</v>
       </c>
       <c r="G21" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>57.9</v>
-      </c>
       <c r="Q21" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8525,48 +8525,48 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8738,25 +8738,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>56.1</v>
+        <v>84.2</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>41.5</v>
+        <v>52.6</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -8765,21 +8765,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -9033,14 +9033,14 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -9049,10 +9049,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9164,44 +9164,48 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q31" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -9435,7 +9439,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9444,48 +9448,44 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>54.2</v>
+        <v>75</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>55.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>42.1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -9526,26 +9526,26 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>57.1</v>
+        <v>52.6</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>50</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9657,25 +9657,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>64.7</v>
+        <v>61.5</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>47.1</v>
+        <v>46.2</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9684,21 +9684,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>69.2</v>
+        <v>42.9</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9728,48 +9728,48 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="N39" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>D/N/U</t>
         </is>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="P39" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -9932,57 +9932,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -10003,19 +10003,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -10023,14 +10023,14 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
         <v>50</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -10050,10 +10050,10 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10083,45 +10083,45 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>87.5</v>
+        <v>80</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q44" s="4" t="n">
         <v>4</v>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10225,25 +10225,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>45.5</v>
+        <v>37.5</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10259,11 +10259,11 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q46" s="4" t="n">
         <v>2</v>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10296,25 +10296,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>58.1</v>
+        <v>62.5</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>51.6</v>
+        <v>43.8</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -10334,10 +10334,10 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10367,25 +10367,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>66.7</v>
+        <v>63.3</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.7</v>
+        <v>51</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10394,21 +10394,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>61.1</v>
+        <v>64</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10520,14 +10520,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10536,21 +10536,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10580,10 +10580,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>54.5</v>
+        <v>76.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10591,14 +10591,14 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54.5</v>
+        <v>41.2</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -10607,21 +10607,21 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10651,48 +10651,48 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>N-D-N-D</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="J52" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>N-D-N-U</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="Q52" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10864,25 +10864,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10894,18 +10894,18 @@
         <v>100</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11219,25 +11219,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>62.9</v>
+        <v>83.3</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11246,21 +11246,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11361,48 +11361,48 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>47.4</v>
+        <v>37.5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>69.2</v>
+        <v>60</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11503,48 +11503,48 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11574,25 +11574,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>51.4</v>
+        <v>47.4</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11601,21 +11601,21 @@
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>58.8</v>
+        <v>77.8</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
         <v>66.7</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -11656,14 +11656,14 @@
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>41.7</v>
+        <v>46.7</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11672,21 +11672,21 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12489,10 +12489,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>54.8</v>
+        <v>64.7</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12500,37 +12500,37 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>42.9</v>
+        <v>58.8</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12560,25 +12560,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>58.3</v>
+        <v>63.2</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>45.8</v>
+        <v>36.8</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12590,18 +12590,18 @@
         <v>50</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12702,48 +12702,48 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
       <c r="G81" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="N81" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I81" s="3" t="n">
+      <c r="P81" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="Q81" s="4" t="n">
         <v>11</v>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q81" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12776,22 +12776,22 @@
         <v>100</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12803,18 +12803,18 @@
         <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -12977,19 +12977,19 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -12997,26 +12997,26 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M85" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -13057,48 +13057,48 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>45.5</v>
+        <v>43.8</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13199,48 +13199,48 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>57.4</v>
+        <v>66.7</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I88" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="P88" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13483,25 +13483,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>54.5</v>
+        <v>37.5</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13510,21 +13510,21 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>50</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13625,10 +13625,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>90</v>
+        <v>54.5</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13636,23 +13636,23 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>70</v>
+        <v>54.5</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N94" s="4" t="n">
         <v>3</v>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>85.7</v>
+        <v>57.1</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -13707,14 +13707,14 @@
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13723,21 +13723,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -13758,34 +13758,34 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -13794,21 +13794,21 @@
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13838,25 +13838,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>58.1</v>
+        <v>72.7</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>48.4</v>
+        <v>40.9</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13865,21 +13865,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>61.5</v>
+        <v>72.7</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>53.8</v>
+        <v>72.7</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13980,37 +13980,37 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>73.7</v>
+        <v>55.6</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>63.2</v>
+        <v>48.1</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>80</v>
+        <v>54.5</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -14018,10 +14018,10 @@
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>80</v>
+        <v>45.5</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14051,25 +14051,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>87.5</v>
+        <v>51.6</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>62.5</v>
+        <v>41.9</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14078,21 +14078,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14122,48 +14122,48 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J101" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="Q101" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J101" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N101" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="Q101" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14264,30 +14264,30 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>76.2</v>
+        <v>72.7</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>47.6</v>
+        <v>45.5</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M103" s="3" t="n">
@@ -14298,11 +14298,11 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q103" s="4" t="n">
         <v>5</v>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>74.5</v>
+        <v>57.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>39.2</v>
+        <v>45.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>70</v>
+        <v>61.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>77.3</v>
+        <v>57.1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>40.9</v>
+        <v>49.4</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>38.9</v>
+        <v>45.5</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>75.3</v>
+        <v>61.4</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>37</v>
+        <v>44.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>41.2</v>
+        <v>43.6</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1797,57 +1797,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
         <v>50</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="n">
-        <v>41.7</v>
+        <v>51.7</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,48 +1928,48 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
         <v>62.5</v>
       </c>
-      <c r="E24" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>42.1</v>
-      </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>59.7</v>
+        <v>62.3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>37.3</v>
+        <v>39.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>60</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.5</v>
+        <v>78</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2244,14 +2244,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>86.7</v>
+        <v>76.3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46.7</v>
+        <v>62.7</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>55.6</v>
+        <v>50.7</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,14 +2610,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>48.1</v>
+        <v>45.2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>62.5</v>
+        <v>46.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,25 +3087,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>58.8</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>38.2</v>
+        <v>64.7</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>69</v>
+        <v>58.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>41.4</v>
+        <v>58.3</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3586,14 +3586,14 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>63.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>59.1</v>
+        <v>55.6</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -3688,57 +3688,57 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N53" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>63.4</v>
+        <v>70.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4135,14 +4135,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>42.1</v>
+        <v>43.2</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>53.8</v>
+        <v>47.4</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>61</v>
+        <v>70.3</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4501,37 +4501,37 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-N</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="n">
         <v>36.4</v>
       </c>
-      <c r="H66" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-D</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>41.7</v>
-      </c>
       <c r="O66" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>56.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>44.6</v>
+        <v>39</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>60.8</v>
+        <v>70.8</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>51</v>
+        <v>45.8</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5416,14 +5416,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>70</v>
+        <v>68.2</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>36</v>
+        <v>59.1</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5477,14 +5477,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>64.7</v>
+        <v>44.4</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5496,18 +5496,18 @@
         <v>66.7</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>65.3</v>
+        <v>53</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5721,14 +5721,14 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>43.1</v>
+        <v>48.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -5740,18 +5740,18 @@
         <v>50</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5832,25 +5832,25 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>43.3</v>
+        <v>41.2</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -5859,21 +5859,21 @@
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>56.5</v>
+        <v>62.5</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>52.2</v>
+        <v>46.9</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>45.3</v>
+        <v>49.3</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,26 +5904,26 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>48</v>
+        <v>43.5</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>43.1</v>
+        <v>44.4</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,25 +5954,25 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>50.6</v>
+        <v>53.7</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>43.7</v>
+        <v>42.9</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>54.7</v>
+        <v>51.3</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>48</v>
+        <v>43.4</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,48 +6015,48 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>51</v>
+        <v>49.2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G91" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N91" s="3" t="n">
-        <v>48.4</v>
+        <v>52.2</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7318,48 +7318,48 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -8161,57 +8161,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>85.7</v>
+        <v>41.7</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>87.5</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>81.2</v>
+        <v>64</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8394,37 +8394,37 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q20" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8525,45 +8525,45 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>2</v>
@@ -8658,57 +8658,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8809,14 +8809,14 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>86.7</v>
+        <v>73.3</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>100</v>
+        <v>73.7</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -9033,14 +9033,14 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>100</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -9049,10 +9049,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9448,44 +9448,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>75</v>
+        <v>54.2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>55.6</v>
+      </c>
       <c r="N35" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q35" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -10003,19 +10007,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -10023,14 +10027,14 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -10042,7 +10046,7 @@
         <v>50</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -10050,10 +10054,10 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -10571,7 +10575,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10580,10 +10584,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>76.5</v>
+        <v>66.7</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -10591,14 +10595,14 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>41.2</v>
+        <v>66.7</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -10614,11 +10618,11 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="Q51" s="4" t="n">
         <v>3</v>
@@ -10713,7 +10717,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10722,25 +10726,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -10749,21 +10753,21 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -11210,7 +11214,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11219,10 +11223,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>83.3</v>
+        <v>55</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11230,14 +11234,14 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>45.8</v>
+        <v>60</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11246,10 +11250,10 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -11257,10 +11261,10 @@
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -11636,7 +11640,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11645,25 +11649,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>66.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46.7</v>
+        <v>38.5</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11672,21 +11676,21 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>44.4</v>
+        <v>75</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -12409,7 +12413,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12418,25 +12422,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>59.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12445,21 +12449,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>64.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -12693,7 +12697,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12702,37 +12706,37 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>72.7</v>
+        <v>50</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12740,10 +12744,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -12764,7 +12768,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12776,7 +12780,7 @@
         <v>100</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -12784,14 +12788,14 @@
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12803,18 +12807,18 @@
         <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -13048,7 +13052,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -13057,7 +13061,7 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="G86" s="4" t="n">
         <v>16</v>
@@ -13068,37 +13072,37 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>43.8</v>
+        <v>56.2</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-D</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>80</v>
+        <v>33.3</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -13190,7 +13194,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -13199,48 +13203,48 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>66.7</v>
+        <v>57.4</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="P88" s="3" t="n">
         <v>44.4</v>
       </c>
-      <c r="J88" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q88" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
@@ -13261,46 +13265,46 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>37.9</v>
+        <v>61.5</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>51.7</v>
+        <v>53.8</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -13308,10 +13312,10 @@
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -13332,7 +13336,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13341,10 +13345,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>61.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13352,14 +13356,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>41.2</v>
+        <v>46.4</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13368,10 +13372,10 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>62.5</v>
+        <v>52.2</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -13379,10 +13383,10 @@
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
@@ -13403,7 +13407,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13412,25 +13416,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>47.5</v>
+        <v>57.9</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>37.5</v>
+        <v>42.1</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13439,21 +13443,21 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,25 +647,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44.4</v>
+        <v>39</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,21 +674,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>55.8</v>
+        <v>59.4</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>44.2</v>
+        <v>45.3</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>57.6</v>
+        <v>52.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>43</v>
+        <v>50.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46</v>
+        <v>42.1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75</v>
+        <v>67.7</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>66.7</v>
+        <v>38.7</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>51.8</v>
+        <v>60.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>69.7</v>
+        <v>65</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61.1</v>
+        <v>51.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>47.2</v>
+        <v>41.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>74.3</v>
+        <v>81.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -963,14 +963,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>51.4</v>
+        <v>40.9</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -979,21 +979,21 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>54.9</v>
+        <v>56.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45.1</v>
+        <v>37.1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>72.7</v>
+        <v>54.5</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>22</v>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>63.6</v>
+        <v>45.5</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>22</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,25 +1196,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>48.8</v>
+        <v>58.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>55.9</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>47.1</v>
+        <v>60</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>52.4</v>
+        <v>55.6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>38.1</v>
+        <v>44.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>46.7</v>
+        <v>100</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>48.5</v>
+        <v>57.1</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>47.3</v>
+        <v>44.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>42.6</v>
+        <v>58.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>50</v>
+        <v>46.3</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,37 +1440,37 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>45.1</v>
+        <v>57.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>48.5</v>
+        <v>43.8</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>62.2</v>
+        <v>73</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>41.5</v>
+        <v>45.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>62.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>47.1</v>
+        <v>58.8</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1634,37 +1634,37 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>52</v>
+        <v>44.1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46.8</v>
+        <v>58.3</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44.9</v>
+        <v>41.3</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46.4</v>
+        <v>37.8</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>40.7</v>
+        <v>37</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>53.7</v>
+        <v>55.4</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>41.5</v>
+        <v>39.3</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1806,25 +1806,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>45.2</v>
+        <v>50</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>52.1</v>
+        <v>43.4</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>42.9</v>
+        <v>69.2</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1867,25 +1867,25 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>74.3</v>
+        <v>65.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>51.4</v>
+        <v>60.9</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1894,21 +1894,21 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>47.1</v>
+        <v>66.7</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,25 +2050,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>57.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>40.6</v>
+        <v>35.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>37.5</v>
+        <v>53.8</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>88.5</v>
+        <v>61</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2244,14 +2244,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.8</v>
+        <v>58.5</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>86.7</v>
+        <v>56</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46.7</v>
+        <v>60</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2294,25 +2294,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>53.3</v>
+        <v>47.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.6</v>
+        <v>45.3</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="O30" s="4" t="n">
         <v>50</v>
-      </c>
-      <c r="O30" s="4" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.9</v>
+        <v>47.9</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>70</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>36.7</v>
+        <v>45.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>73.3</v>
+        <v>62.2</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>61.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>55.4</v>
+        <v>42.3</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>68.8</v>
+        <v>66.7</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,48 +2538,48 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>58.3</v>
+        <v>51.4</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>39.4</v>
+        <v>40.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K34" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L34" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>39.1</v>
-      </c>
       <c r="O34" s="4" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -2590,34 +2590,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>46.6</v>
+        <v>50.8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46.6</v>
+        <v>55.4</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>48.5</v>
+        <v>56.2</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>42.4</v>
+        <v>56.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>53.2</v>
+        <v>60</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2671,37 +2671,37 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46.8</v>
+        <v>43.3</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>47.4</v>
+        <v>58.6</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2732,14 +2732,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46.8</v>
+        <v>36.8</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>44.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.1</v>
+        <v>43.6</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,26 +2854,26 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>51.4</v>
+        <v>48.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>53.8</v>
+        <v>48</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,25 +2904,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>40.5</v>
+        <v>49.3</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>66.7</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>66.7</v>
+        <v>51.4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,48 +3026,48 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>36</v>
+        <v>41.7</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L42" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="O42" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,25 +3087,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>81.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>37.5</v>
+        <v>44.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>80</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,25 +3148,25 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>63.2</v>
+        <v>68.8</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>52.6</v>
+        <v>61.9</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>42.1</v>
+        <v>38.1</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>52.9</v>
+        <v>51.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3281,14 +3281,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>43.9</v>
+        <v>45</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>47.2</v>
+        <v>42.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>41.5</v>
+        <v>49.3</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>55.2</v>
+        <v>55.7</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>43.6</v>
+        <v>41.4</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>64.5</v>
+        <v>56.5</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>44.7</v>
+        <v>39.1</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,25 +3392,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>51.6</v>
+        <v>45.1</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>45.2</v>
+        <v>40.9</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>55</v>
+        <v>42.7</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>45</v>
+        <v>48.8</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,25 +3453,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>52.1</v>
+        <v>58.7</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>41.5</v>
+        <v>46.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>50.8</v>
+        <v>61.8</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>39.7</v>
+        <v>47.1</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>66.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>64</v>
+        <v>59.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>92.3</v>
+        <v>60.9</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>46.2</v>
+        <v>47.8</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>68.5</v>
+        <v>59.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>35.2</v>
+        <v>40.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>62.5</v>
+        <v>53.6</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>65.8</v>
+        <v>52.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,21 +3846,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>47.1</v>
+        <v>57.1</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,48 +4002,48 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>58.6</v>
+        <v>61.2</v>
       </c>
       <c r="E58" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-D</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="H58" s="4" t="n">
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="O58" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>39.1</v>
+        <v>37</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>56.8</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>55.6</v>
+        <v>44.9</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>46.2</v>
+        <v>48.1</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,48 +4368,48 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>61.4</v>
+        <v>45</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>44.3</v>
+        <v>45</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>74.7</v>
+        <v>66.7</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>50.7</v>
+        <v>43.9</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="L65" s="4" t="n">
         <v>18</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="O65" s="4" t="n">
         <v>18</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>53.2</v>
+        <v>38.2</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>90.5</v>
+        <v>57.9</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>61.9</v>
+        <v>42.1</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
@@ -4542,49 +4542,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="E67" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>85.7</v>
+      </c>
       <c r="H67" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="L67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="O67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4839,57 +4847,57 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="n">
         <v>51.9</v>
       </c>
-      <c r="E72" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>54.5</v>
-      </c>
       <c r="O72" s="4" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73">
@@ -4961,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4970,25 +4978,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>55.2</v>
+        <v>50.9</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>53.4</v>
+        <v>43.4</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4997,21 +5005,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>60</v>
+        <v>49.2</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>46.7</v>
+        <v>50.8</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5031,10 +5039,10 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5042,14 +5050,14 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5061,18 +5069,18 @@
         <v>100</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5092,25 +5100,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>46.6</v>
+        <v>41.1</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5119,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5153,25 +5161,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>38.5</v>
+        <v>47.6</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5180,21 +5188,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>58.6</v>
+        <v>68.8</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>44.8</v>
+        <v>59.4</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5214,25 +5222,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>62.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>37.5</v>
+        <v>46.1</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5241,10 +5249,10 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5252,10 +5260,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5275,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>63.3</v>
+        <v>58.9</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>49.4</v>
+        <v>46.7</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5302,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>66.7</v>
+        <v>62.1</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>59.3</v>
+        <v>34.5</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
@@ -5388,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5397,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>59.5</v>
+        <v>62.1</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5408,14 +5416,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>40.5</v>
+        <v>43.1</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5424,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>61.1</v>
+        <v>62.5</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>44.4</v>
+        <v>45.8</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82">
@@ -5510,7 +5518,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5519,25 +5527,25 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5546,10 +5554,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5557,10 +5565,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>38.3</v>
+        <v>45.2</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5580,10 +5588,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>68.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5591,14 +5599,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>41.3</v>
+        <v>44.2</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5607,21 +5615,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>52.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>42.9</v>
+        <v>47.4</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
@@ -5693,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5702,37 +5710,37 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>52.4</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>47.6</v>
+        <v>44.7</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>47.5</v>
+        <v>66.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5740,10 +5748,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5763,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>38.2</v>
+        <v>41.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5790,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>46.4</v>
+        <v>45.6</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
@@ -5998,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6007,25 +6015,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>55.7</v>
+        <v>56.9</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>47.1</v>
+        <v>35.3</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6034,21 +6042,21 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>57.1</v>
+        <v>53.8</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6068,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>48.4</v>
+        <v>64.8</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>53.1</v>
+        <v>41.6</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6095,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>60.9</v>
+        <v>72.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>52.2</v>
+        <v>45.1</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93">
@@ -6181,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6190,25 +6198,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>68.2</v>
+        <v>66.2</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>51.8</v>
+        <v>39.4</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6217,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>54.5</v>
+        <v>61.5</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>59.1</v>
+        <v>46.2</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6251,10 +6259,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>62.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6262,14 +6270,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>41</v>
+        <v>45.9</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6278,21 +6286,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>57.5</v>
+        <v>81.2</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
@@ -6364,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6373,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6384,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.8</v>
+        <v>43</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6400,10 +6408,10 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>58.6</v>
+        <v>51.1</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6411,10 +6419,10 @@
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>44.8</v>
+        <v>40.4</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98">
@@ -6486,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6495,48 +6503,48 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>53.8</v>
+        <v>61.9</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-N</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="n">
         <v>42.9</v>
       </c>
-      <c r="H99" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="n">
-        <v>45.2</v>
-      </c>
       <c r="O99" s="4" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6556,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>60.5</v>
+        <v>64</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>40.7</v>
+        <v>44.2</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6583,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>59.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>40.6</v>
+        <v>44.3</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101">
@@ -6852,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6861,25 +6869,25 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>55.1</v>
+        <v>53.2</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>44.9</v>
+        <v>48</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6891,18 +6899,18 @@
         <v>52.9</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7159,7 +7167,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7168,10 +7176,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7179,26 +7187,26 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>44.4</v>
+        <v>53.8</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -7206,10 +7214,10 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>55.6</v>
+        <v>46.2</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -7230,19 +7238,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>51.7</v>
+        <v>43.8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7250,26 +7258,26 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>37.9</v>
+        <v>50</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -7277,10 +7285,10 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -7301,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7310,10 +7318,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>62.5</v>
+        <v>61.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7321,37 +7329,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>43.8</v>
+        <v>51.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -7372,19 +7380,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45.8</v>
+        <v>44.4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7392,37 +7400,37 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>45.8</v>
+        <v>61.1</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -7443,34 +7451,34 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7514,7 +7522,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7526,41 +7534,45 @@
         <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7581,7 +7593,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7590,25 +7602,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7617,10 +7629,10 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -7628,10 +7640,10 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7794,19 +7806,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>47.1</v>
+        <v>100</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7814,37 +7826,33 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7865,7 +7873,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7874,48 +7882,44 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8007,7 +8011,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8016,48 +8020,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>40</v>
+        <v>54.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>51.4</v>
+        <v>63.6</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>66.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -8078,57 +8082,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>61.5</v>
-      </c>
       <c r="Q16" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -8220,57 +8224,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>42.3</v>
+        <v>38.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>62.5</v>
+        <v>44.4</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -8291,7 +8295,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8300,10 +8304,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>59.1</v>
+        <v>50</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8311,14 +8315,14 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8327,21 +8331,21 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -8362,7 +8366,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8371,25 +8375,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>35</v>
+        <v>45.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8398,21 +8402,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -8433,7 +8437,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8442,10 +8446,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>63.6</v>
+        <v>53.3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -8453,14 +8457,14 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>45.5</v>
+        <v>46.7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8469,21 +8473,21 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -8504,16 +8508,16 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>12</v>
@@ -8531,19 +8535,19 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -8551,10 +8555,10 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -8575,7 +8579,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8584,48 +8588,48 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J23" s="4" t="n">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8784,34 +8788,34 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -8820,21 +8824,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -8997,7 +9001,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9006,10 +9010,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -9017,37 +9021,37 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -9068,7 +9072,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9077,25 +9081,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>43.5</v>
+        <v>57.7</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>43.5</v>
+        <v>46.2</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -9111,11 +9115,11 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="Q30" s="4" t="n">
         <v>9</v>
@@ -9139,7 +9143,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9148,48 +9152,48 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -9210,7 +9214,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9219,25 +9223,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>52.9</v>
+        <v>62.1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>41.2</v>
+        <v>51.7</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9246,21 +9250,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>55.6</v>
+        <v>62.5</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -9281,7 +9285,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9290,25 +9294,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9317,21 +9321,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -9352,34 +9356,34 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>52.4</v>
+        <v>44</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>61.9</v>
+        <v>48</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -9388,10 +9392,10 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>70</v>
+        <v>57.1</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -9399,10 +9403,10 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
@@ -9423,57 +9427,57 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>47.1</v>
+        <v>52.4</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>47.1</v>
+        <v>81</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>44.4</v>
+        <v>53.8</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>55.6</v>
+        <v>92.3</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
@@ -9494,19 +9498,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -9514,14 +9518,14 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9533,18 +9537,18 @@
         <v>66.7</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -9565,19 +9569,19 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>37.1</v>
+        <v>57.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9585,37 +9589,37 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>48.6</v>
+        <v>42.9</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -9707,7 +9711,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9716,25 +9720,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>53.3</v>
+        <v>46.9</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9743,21 +9747,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -9778,19 +9782,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>40</v>
+        <v>63.6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9798,34 +9802,34 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q40" s="4" t="n">
         <v>3</v>
@@ -9849,57 +9853,57 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>50</v>
+        <v>54.8</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>50</v>
+        <v>72.2</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -9920,57 +9924,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -9991,7 +9995,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10000,10 +10004,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -10011,14 +10015,14 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -10034,7 +10038,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
@@ -10062,34 +10066,34 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>80</v>
+        <v>44.4</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -10098,21 +10102,21 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -10204,57 +10208,57 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>60.9</v>
+        <v>44.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>56.5</v>
+        <v>44.4</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -10275,57 +10279,57 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>52</v>
+        <v>47.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>60</v>
+        <v>47.6</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -10346,34 +10350,34 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>53.5</v>
+        <v>47.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>48.8</v>
+        <v>47.8</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10382,10 +10386,10 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>66.7</v>
+        <v>45.8</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -10393,10 +10397,10 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
@@ -10417,19 +10421,19 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -10437,37 +10441,37 @@
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>48</v>
+        <v>43.8</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>63.6</v>
+        <v>57.1</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -10488,7 +10492,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10497,10 +10501,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -10508,14 +10512,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10527,18 +10531,18 @@
         <v>75</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -10559,7 +10563,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10568,25 +10572,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -10595,21 +10599,21 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -10630,7 +10634,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10639,10 +10643,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>64.3</v>
+        <v>54.5</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -10650,37 +10654,37 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -10843,19 +10847,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>61.1</v>
+        <v>55.6</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10863,37 +10867,37 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>55.6</v>
+        <v>59.3</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -11056,7 +11060,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11065,10 +11069,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -11076,14 +11080,14 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>57.1</v>
+        <v>53.3</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -11092,21 +11096,21 @@
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -11198,7 +11202,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11207,48 +11211,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>64.3</v>
+        <v>75</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -11269,7 +11273,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11278,48 +11282,48 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
@@ -11478,19 +11482,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>58.3</v>
+        <v>45.2</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -11498,37 +11502,37 @@
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>50</v>
+        <v>54.8</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -11549,46 +11553,46 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
         </is>
       </c>
       <c r="M65" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -11596,10 +11600,10 @@
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -11620,54 +11624,54 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46.4</v>
+        <v>38.5</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>5</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>5</v>
@@ -11691,30 +11695,34 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -12038,46 +12046,46 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G72" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="J72" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -12085,10 +12093,10 @@
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -12180,19 +12188,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12200,26 +12208,26 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>42.9</v>
+        <v>48.7</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>85.7</v>
+        <v>43.8</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -12227,10 +12235,10 @@
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -12251,7 +12259,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12263,41 +12271,45 @@
         <v>100</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q75" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -12318,57 +12330,57 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -12389,7 +12401,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12398,48 +12410,48 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>60</v>
+        <v>64.3</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -12460,53 +12472,57 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G78" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="J78" s="4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="N78" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="Q78" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -12527,7 +12543,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12536,48 +12552,48 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G79" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q79" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -12669,7 +12685,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12678,25 +12694,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12708,18 +12724,18 @@
         <v>100</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -12807,46 +12823,46 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>44</v>
+        <v>51.6</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>44</v>
+        <v>58.1</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>41.7</v>
+        <v>53.3</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -12854,10 +12870,10 @@
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
@@ -12878,7 +12894,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12887,48 +12903,48 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>57.1</v>
+        <v>63.6</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -13020,34 +13036,34 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>38.5</v>
+        <v>75</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -13056,10 +13072,10 @@
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -13067,10 +13083,10 @@
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -13091,7 +13107,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13100,10 +13116,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -13111,14 +13127,14 @@
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>52.6</v>
+        <v>48</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13127,21 +13143,21 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -13375,57 +13391,57 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -13446,7 +13462,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13455,10 +13471,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>56.2</v>
+        <v>59.1</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13466,14 +13482,14 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>43.8</v>
+        <v>40.9</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13489,7 +13505,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
@@ -13588,7 +13604,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13597,10 +13613,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13608,37 +13624,37 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-U</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J94" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>N-N-D-D</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="N94" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -13659,19 +13675,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -13679,14 +13695,14 @@
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13695,21 +13711,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -13801,57 +13817,57 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N97" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J97" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="n">
-        <v>37.5</v>
-      </c>
       <c r="Q97" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -13943,34 +13959,34 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>39.3</v>
+        <v>60</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13979,21 +13995,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N99" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N99" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>70</v>
-      </c>
       <c r="Q99" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -14014,57 +14030,57 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>56.2</v>
+        <v>46.2</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>56.2</v>
+        <v>53.8</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
@@ -14369,46 +14385,46 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>46.2</v>
+        <v>38.5</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I105" s="3" t="n">
         <v>46.2</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -14416,10 +14432,10 @@
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,48 +952,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>67.5</v>
+        <v>81.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-N</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-D</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>33.3</v>
-      </c>
       <c r="O8" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>54.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45.1</v>
+        <v>38.5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>72.7</v>
+        <v>56.5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>63.6</v>
+        <v>47.8</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>58.8</v>
+        <v>47.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1634,37 +1634,37 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>44.1</v>
+        <v>52</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>58.3</v>
+        <v>46.8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44.9</v>
+        <v>45.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46.4</v>
+        <v>47.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1806,25 +1806,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>52.6</v>
+        <v>52.1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,48 +1928,48 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.5</v>
+        <v>58.6</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>43.8</v>
+        <v>51.7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,25 +2599,25 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>62.5</v>
+        <v>50.8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>66.7</v>
+        <v>51.4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,25 +3087,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>81.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>37.5</v>
+        <v>44.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,21 +3114,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>80</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,48 +3270,48 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>59.2</v>
+        <v>51.2</v>
       </c>
       <c r="E46" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="L46" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="H46" s="4" t="n">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="O46" s="4" t="n">
         <v>71</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>52.6</v>
+        <v>51.6</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46.1</v>
+        <v>45.2</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>48.1</v>
+        <v>55</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>66.2</v>
+        <v>63</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>39.7</v>
+        <v>45.7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>64</v>
+        <v>59.6</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>40</v>
+        <v>43.9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>65.8</v>
+        <v>51.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>44.3</v>
+        <v>45.3</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,21 +3846,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>58.8</v>
+        <v>54.8</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>47.1</v>
+        <v>48.4</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3880,48 +3880,48 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.5</v>
+        <v>47.2</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="K56" s="3" t="n">
-        <v>57.1</v>
+        <v>46.7</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>57.1</v>
+        <v>53.3</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>56.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>44.9</v>
+        <v>55.6</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>51.9</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>48.1</v>
+        <v>46.2</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>74.7</v>
+        <v>66.7</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>50.7</v>
+        <v>43.9</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="L65" s="4" t="n">
         <v>18</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="O65" s="4" t="n">
         <v>18</v>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,25 +4734,25 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>58.1</v>
+        <v>66.7</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>38.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71">
@@ -4847,57 +4847,57 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="N72" s="3" t="n">
         <v>51.9</v>
       </c>
-      <c r="E72" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="L72" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>54.5</v>
-      </c>
       <c r="O72" s="4" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,25 +4917,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>55.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>45.3</v>
+        <v>51.2</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>52.3</v>
+        <v>75</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>47.7</v>
+        <v>50</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5039,25 +5039,25 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5069,18 +5069,18 @@
         <v>100</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>36.1</v>
+        <v>38.5</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>66.7</v>
+        <v>58.6</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>47.6</v>
+        <v>44.8</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5710,48 +5710,48 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>U-N-U-U</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
           <t>U</t>
         </is>
       </c>
-      <c r="G86" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>U-N-U-N</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="L86" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N86" s="3" t="n">
-        <v>44.4</v>
+        <v>37.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>48.4</v>
+        <v>55.6</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6087,14 +6087,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>53.1</v>
+        <v>45</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>60.9</v>
+        <v>48</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>52.2</v>
+        <v>42</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>42.3</v>
+        <v>38.9</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>76.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-D</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Cumartesi</t>
+          <t>Pazar</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44.3</v>
+        <v>42.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75</v>
+        <v>81.7</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>40.6</v>
+        <v>45</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>51.8</v>
+        <v>60.9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42.9</v>
+        <v>48.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>48.4</v>
+        <v>57.4</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>50</v>
+        <v>59.6</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -963,37 +963,37 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>54.9</v>
+        <v>57</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>43.4</v>
+        <v>43</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>52.9</v>
+        <v>51.4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44.1</v>
+        <v>45.9</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>66.3</v>
+        <v>70</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1085,14 +1085,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>41.9</v>
+        <v>40</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>61.1</v>
+        <v>73.7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>44.4</v>
+        <v>47.4</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>66.3</v>
+        <v>55.9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>40.4</v>
+        <v>44.1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>43.3</v>
+        <v>38.9</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,37 +1196,37 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>49.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>49.4</v>
+        <v>44.6</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>59.5</v>
+        <v>54.3</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,25 +1318,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>64.3</v>
+        <v>64</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40.7</v>
+        <v>36.8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>52.8</v>
+        <v>55.8</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>47.2</v>
+        <v>44.2</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>48.3</v>
+        <v>66.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>46.4</v>
+        <v>37.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>52.8</v>
+        <v>53.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>48.6</v>
+        <v>42.3</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>53.6</v>
+        <v>53.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>47.5</v>
+        <v>42.6</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>55.8</v>
+        <v>54.8</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>48.8</v>
+        <v>41.9</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>62.6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.1</v>
+        <v>42.7</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>62.7</v>
+        <v>58.9</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>45.1</v>
+        <v>46.4</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60.6</v>
+        <v>55.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>48.5</v>
+        <v>46.9</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>58.3</v>
+        <v>49.1</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>58.3</v>
+        <v>54.7</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.5</v>
+        <v>59.2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>38.9</v>
+        <v>44.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>61.1</v>
+        <v>55</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>41.7</v>
+        <v>47.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,25 +1928,25 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>60.9</v>
+        <v>57.6</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44.9</v>
+        <v>50.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>53.3</v>
+        <v>45.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>43.3</v>
+        <v>40.9</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,48 +2050,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>59.8</v>
+        <v>55.1</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>42.7</v>
+        <v>51.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>78.3</v>
+        <v>40.9</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -2102,57 +2102,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>54.2</v>
+        <v>44.4</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45.8</v>
+        <v>48.1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>60.8</v>
+        <v>58.1</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2183,14 +2183,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>47.5</v>
+        <v>43.8</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>57.9</v>
+        <v>65.2</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46.1</v>
+        <v>43.9</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>67.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,18 +2382,18 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>60.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>23</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>34.8</v>
+        <v>52.2</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>23</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59.6</v>
+        <v>56.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.1</v>
+        <v>42.3</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,21 +2504,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>63.2</v>
+        <v>51.9</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2538,25 +2538,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>60</v>
+        <v>54.8</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>66.7</v>
+        <v>53.6</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>44.4</v>
+        <v>53.6</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,25 +2660,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>47.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46.5</v>
+        <v>36.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>51.4</v>
+        <v>57.1</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>45.1</v>
+        <v>57.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46.4</v>
+        <v>37.7</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>44.6</v>
+        <v>59.3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>53.6</v>
+        <v>59.3</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>67.3</v>
+        <v>52</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2793,14 +2793,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>41.8</v>
+        <v>46.7</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>65.2</v>
+        <v>50</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>34.8</v>
+        <v>50</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,25 +2904,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>60.9</v>
+        <v>61.1</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>47.8</v>
+        <v>38.9</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>57.6</v>
+        <v>60</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>77.8</v>
+        <v>61.7</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>50</v>
+        <v>44.7</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>87.5</v>
+        <v>52.2</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>62.5</v>
+        <v>47.8</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -3200,19 +3200,19 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>46.3</v>
+        <v>54.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3220,14 +3220,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>48.1</v>
+        <v>39.2</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3236,21 +3236,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>48.1</v>
+        <v>54.5</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>55.6</v>
+        <v>45.5</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60.2</v>
+        <v>75</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46.6</v>
+        <v>42.2</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>64.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>45.1</v>
+        <v>43.5</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>42.9</v>
+        <v>48.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46.5</v>
+        <v>53.1</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>65</v>
+        <v>83.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3586,37 +3586,37 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,25 +3636,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>57.6</v>
+        <v>58.6</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45.6</v>
+        <v>40.6</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>50</v>
+        <v>62.9</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46.9</v>
+        <v>51.4</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>47.6</v>
+        <v>51.1</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,26 +3830,26 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>47.8</v>
+        <v>45.8</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46.3</v>
+        <v>48.6</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>61.9</v>
+        <v>66.7</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>40</v>
+        <v>44.8</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>52</v>
@@ -4135,14 +4135,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>38.5</v>
+        <v>44.2</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>52</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>62.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45.8</v>
+        <v>54.3</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>55.6</v>
+        <v>93.3</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>55.6</v>
+        <v>46.7</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,25 +4246,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>66.7</v>
+        <v>81</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>44.4</v>
+        <v>52.4</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>76.2</v>
+        <v>77.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>47.6</v>
+        <v>55.6</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4318,14 +4318,14 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>61.5</v>
+        <v>56.2</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>49.2</v>
+        <v>52.9</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -4379,14 +4379,14 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>43.7</v>
+        <v>47.1</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>50.6</v>
+        <v>47.6</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>46.9</v>
+        <v>52.4</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4623,14 +4623,14 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4639,21 +4639,21 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>60.9</v>
+        <v>100</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>43.5</v>
+        <v>62.5</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,48 +4673,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>44.4</v>
+        <v>64.3</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4847,46 +4847,46 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>51.9</v>
+        <v>46.6</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>51.9</v>
+        <v>47.5</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>54.5</v>
+        <v>49.1</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>54.5</v>
+        <v>50.9</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,25 +4917,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>62.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>64.3</v>
+        <v>72.7</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>54.4</v>
+        <v>47.6</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4989,14 +4989,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>46.7</v>
+        <v>42</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>45.3</v>
+        <v>52.2</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>45.3</v>
+        <v>42</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>62.2</v>
+        <v>66.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>40</v>
+        <v>47.9</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>62.1</v>
+        <v>73.7</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>41.4</v>
+        <v>57.9</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,25 +5405,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>56.1</v>
+        <v>85.7</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>50</v>
+        <v>35.7</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>56.5</v>
+        <v>80</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>52.2</v>
+        <v>40</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,37 +5466,37 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>56</v>
+        <v>43.2</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>59.1</v>
+        <v>63.5</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>42.4</v>
+        <v>43.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>51.6</v>
+        <v>58.8</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>38.7</v>
+        <v>47.1</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,25 +5893,25 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>59.6</v>
+        <v>57.6</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>50.9</v>
+        <v>39.4</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>54.2</v>
+        <v>70</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,25 +5954,25 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>38.6</v>
+        <v>42.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>38.2</v>
+        <v>44.4</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,48 +6137,48 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>49.4</v>
+        <v>64</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.8</v>
+        <v>44</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>57.1</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>44.2</v>
+        <v>50</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,25 +6259,25 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>44.6</v>
+        <v>53.3</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>52.9</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>52.9</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,25 +6320,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>43.9</v>
+        <v>35</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>64.3</v>
+        <v>46.7</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,14 +6697,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>42.4</v>
+        <v>44.4</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>38.9</v>
+        <v>42.9</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>47.8</v>
+        <v>55.1</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6880,14 +6880,14 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>42.9</v>
+        <v>44.9</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
-        <v>51.8</v>
+        <v>50</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>43.4</v>
+        <v>55</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>73.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7329,14 +7329,14 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>47.4</v>
+        <v>42.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7345,21 +7345,21 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>100</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7400,14 +7400,14 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>57.1</v>
+        <v>63.6</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>42.9</v>
+        <v>63.6</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7542,37 +7542,33 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7593,7 +7589,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7602,10 +7598,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>53.6</v>
+        <v>80</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7613,37 +7609,37 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-D</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-U</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>44.4</v>
-      </c>
       <c r="Q9" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -7664,7 +7660,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,48 +7669,48 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>N-D-N-D</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>N-D-N-U</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="Q10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7735,7 +7731,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7744,25 +7740,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45.5</v>
+        <v>53.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.5</v>
+        <v>43.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7771,10 +7767,10 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -7782,10 +7778,10 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -7806,7 +7802,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,10 +7811,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7826,37 +7822,37 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>60.7</v>
+        <v>58.3</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -7948,7 +7944,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,10 +7953,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>77.3</v>
+        <v>52.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7968,14 +7964,14 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>40.9</v>
+        <v>47.6</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7984,10 +7980,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7995,10 +7991,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -8090,7 +8086,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8099,10 +8095,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>57.6</v>
+        <v>69.2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -8110,14 +8106,14 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8126,21 +8122,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>47.1</v>
+        <v>62.5</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -8161,7 +8157,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8170,10 +8166,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>54.2</v>
+        <v>52.2</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -8181,14 +8177,14 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>47.9</v>
+        <v>39.1</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8197,10 +8193,10 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>57.9</v>
+        <v>66.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8204,10 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -8232,7 +8228,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8241,48 +8237,48 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>65.2</v>
+        <v>53.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>63.6</v>
+        <v>37.5</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>45.5</v>
+        <v>62.5</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -8303,7 +8299,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8312,10 +8308,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8323,14 +8319,14 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8339,10 +8335,10 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8350,10 +8346,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -8374,7 +8370,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,7 +8379,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>16</v>
@@ -8394,14 +8390,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8410,21 +8406,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -8654,7 +8650,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8663,48 +8659,48 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -8796,7 +8792,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8805,48 +8801,48 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-D</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>37.5</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>N-N-D-U</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q26" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -8867,19 +8863,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -8890,34 +8886,34 @@
         <v>50</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -8938,7 +8934,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8947,10 +8943,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8958,26 +8954,26 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>53.8</v>
+        <v>61.5</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -8985,10 +8981,10 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -9151,7 +9147,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9160,25 +9156,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -9194,11 +9190,11 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q31" s="4" t="n">
         <v>5</v>
@@ -9293,7 +9289,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9309,18 +9305,18 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9329,21 +9325,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -9364,7 +9360,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -9373,34 +9369,34 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>93.8</v>
+        <v>53.3</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>43.8</v>
+        <v>46.7</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>5</v>
@@ -9506,57 +9502,49 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>54.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>63.6</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>77.8</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>44.4</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr"/>
       <c r="Q36" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -9577,7 +9565,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9586,10 +9574,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9597,14 +9585,14 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>51.4</v>
+        <v>77.8</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9613,10 +9601,10 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -9624,10 +9612,10 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -9648,7 +9636,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9657,48 +9645,48 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -9790,7 +9778,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9799,48 +9787,44 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr"/>
       <c r="Q40" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -10074,7 +10058,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10083,25 +10067,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -10110,21 +10094,21 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -10145,7 +10129,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10154,10 +10138,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -10165,37 +10149,37 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>51.5</v>
+        <v>44.4</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -10358,7 +10342,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10367,10 +10351,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -10378,26 +10362,26 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-N</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J48" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-U</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>90.5</v>
-      </c>
       <c r="N48" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -10405,10 +10389,10 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -10500,7 +10484,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10509,25 +10493,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>74.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>48.4</v>
+        <v>38.5</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10536,10 +10520,10 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -10550,7 +10534,7 @@
         <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -10571,57 +10555,49 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10642,7 +10618,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10651,25 +10627,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>72</v>
+        <v>73.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10678,21 +10654,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -10855,7 +10831,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10864,10 +10840,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>52.8</v>
+        <v>66.7</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10875,37 +10851,37 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>55.6</v>
+        <v>51.9</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N55" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n">
-        <v>41.7</v>
-      </c>
       <c r="Q55" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -11068,7 +11044,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11077,10 +11053,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>61.5</v>
+        <v>58.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -11088,37 +11064,37 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>46.2</v>
+        <v>52.9</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -11210,7 +11186,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11219,10 +11195,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>61.5</v>
+        <v>100</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11230,14 +11206,14 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11277,7 +11253,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11286,25 +11262,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -11313,21 +11289,21 @@
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -11348,7 +11324,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11357,48 +11333,44 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr"/>
       <c r="Q62" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -11419,7 +11391,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -11428,14 +11400,14 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
@@ -11446,26 +11418,30 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N63" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q63" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -11486,7 +11462,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11495,25 +11471,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>57.1</v>
+        <v>53.3</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>64.3</v>
+        <v>40</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -11522,21 +11498,21 @@
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -11770,7 +11746,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11779,25 +11755,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11806,21 +11782,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -11841,19 +11817,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11861,37 +11837,33 @@
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n">
-        <v>40</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr"/>
       <c r="Q69" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -12054,46 +12026,46 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N72" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -12101,10 +12073,10 @@
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -12125,7 +12097,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12134,48 +12106,48 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>57.1</v>
+        <v>90</v>
       </c>
       <c r="G73" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-D</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N73" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="n">
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="Q73" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q73" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -12196,7 +12168,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12205,10 +12177,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>57.4</v>
+        <v>58.1</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12216,14 +12188,14 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>42.6</v>
+        <v>45.2</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12232,21 +12204,21 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>45</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -12409,7 +12381,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12418,10 +12390,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -12429,14 +12401,14 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>57.1</v>
+        <v>61.5</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12445,21 +12417,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -12693,57 +12665,57 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -12764,7 +12736,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12773,48 +12745,48 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -13119,7 +13091,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13128,25 +13100,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>69.2</v>
+        <v>57.6</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13155,10 +13127,10 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13166,10 +13138,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -13261,57 +13233,57 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -13332,7 +13304,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13341,48 +13313,48 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>66.7</v>
+        <v>58.1</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>72.2</v>
+        <v>46.5</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>63.6</v>
+        <v>47.4</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>63.6</v>
+        <v>42.1</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
@@ -13545,46 +13517,46 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>48.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>43.2</v>
+        <v>58.8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -13595,7 +13567,7 @@
         <v>50</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -13687,7 +13659,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13696,25 +13668,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>60.9</v>
+        <v>80</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>52.2</v>
+        <v>60</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13723,21 +13695,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -13758,7 +13730,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -13770,45 +13742,45 @@
         <v>50</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -14184,7 +14156,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14193,25 +14165,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14220,21 +14192,21 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -14255,7 +14227,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14264,48 +14236,48 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -14397,7 +14369,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -14406,48 +14378,48 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>58.6</v>
+        <v>55.6</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I105" s="3" t="n">
-        <v>48.3</v>
+        <v>66.7</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>43</v>
+        <v>45.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>46.8</v>
+        <v>44.9</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,48 +952,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>81.8</v>
+        <v>63</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1268,14 +1268,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>59.1</v>
+        <v>48.1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>60</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>70</v>
+        <v>53.8</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>66.7</v>
+        <v>48.3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>37.7</v>
+        <v>46.4</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>53.8</v>
+        <v>52.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>42.3</v>
+        <v>48.6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,25 +2660,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36.8</v>
+        <v>50.6</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>57.1</v>
+        <v>45.7</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>42.9</v>
+        <v>48.6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,25 +2721,25 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>57.4</v>
+        <v>45.1</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>37.7</v>
+        <v>46.4</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>59.3</v>
+        <v>44.6</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>59.3</v>
+        <v>53.6</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,25 +2904,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>38.9</v>
+        <v>47.8</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>60</v>
+        <v>57.6</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,37 +3026,37 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>45.8</v>
+        <v>64.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3098,14 +3098,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45.7</v>
+        <v>54.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>54.1</v>
+        <v>50.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3220,14 +3220,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>39.2</v>
+        <v>43.9</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3236,21 +3236,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>54.5</v>
+        <v>53.6</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>50.3</v>
+        <v>63.9</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>44.3</v>
+        <v>50</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>46.5</v>
+        <v>60.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>49.3</v>
+        <v>54.5</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>75</v>
+        <v>60.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.2</v>
+        <v>46.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>43.5</v>
+        <v>45.1</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3700,22 +3700,22 @@
         <v>66.7</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>64.3</v>
+        <v>80</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>40</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>69</v>
+        <v>59.6</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>38.1</v>
+        <v>47.2</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>66.7</v>
+        <v>55</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>38.9</v>
+        <v>40</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,25 +4246,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>81</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>52.4</v>
+        <v>45.6</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>77.8</v>
+        <v>88.2</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>55.6</v>
+        <v>47.1</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,48 +4368,48 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>52.9</v>
+        <v>42.5</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>47.6</v>
+        <v>46.2</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>49.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4501,14 +4501,14 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>39.4</v>
+        <v>51.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>50</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4551,25 +4551,25 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>72.2</v>
+        <v>54.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4612,25 +4612,25 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>62.5</v>
+        <v>48.4</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,25 +4673,25 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E69" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>64.3</v>
-      </c>
       <c r="H69" s="4" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -4703,18 +4703,18 @@
         <v>100</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>46.6</v>
+        <v>45.1</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4867,14 +4867,14 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>49.1</v>
+        <v>51</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5039,25 +5039,25 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>80</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>47.9</v>
+        <v>40</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>73.7</v>
+        <v>62.1</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>57.9</v>
+        <v>41.4</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,25 +5405,25 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>85.7</v>
+        <v>61.2</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>35.7</v>
+        <v>46.3</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,37 +5466,37 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.2</v>
+        <v>56</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>63.5</v>
+        <v>59.1</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>43.6</v>
+        <v>42.4</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>58.8</v>
+        <v>51.6</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>47.1</v>
+        <v>38.7</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,25 +5954,25 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>56.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>42.6</v>
+        <v>38.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>50</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>44.4</v>
+        <v>38.2</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>64</v>
+        <v>54.7</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -6148,14 +6148,14 @@
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>44</v>
+        <v>43.1</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>50</v>
+        <v>38.7</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>90</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>53.3</v>
+        <v>43.1</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>43.8</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,25 +6320,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>46.7</v>
+        <v>53.8</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>46.7</v>
+        <v>38.5</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>52.4</v>
+        <v>60.5</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6575,14 +6575,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>42.9</v>
+        <v>40.7</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L100" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="n">
-        <v>46.1</v>
-      </c>
       <c r="O100" s="4" t="n">
-        <v>76</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,25 +6869,25 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>55.1</v>
+        <v>53.4</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>44.9</v>
+        <v>47.7</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
-        <v>50</v>
+        <v>55.7</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>55</v>
+        <v>47.1</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7105,25 +7105,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>67.5</v>
+        <v>80</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>69.2</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>78.3</v>
+        <v>80</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7187,14 +7187,14 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>47.8</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="Q3" s="4" t="n">
         <v>9</v>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7534,41 +7534,45 @@
         <v>100</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-D</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-N</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7873,12 +7877,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
@@ -7900,7 +7904,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7916,11 +7920,11 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="4" t="n">
         <v>2</v>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8095,10 +8099,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>69.2</v>
+        <v>57.6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -8106,14 +8110,14 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46.2</v>
+        <v>54.5</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8122,21 +8126,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>62.5</v>
+        <v>47.1</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -9502,49 +9506,57 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>42.9</v>
+      </c>
       <c r="G36" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J36" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>33.3</v>
+      </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q36" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -9565,7 +9577,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9574,10 +9586,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9585,14 +9597,14 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>77.8</v>
+        <v>51.4</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9601,10 +9613,10 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -9612,10 +9624,10 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -9778,7 +9790,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9787,44 +9799,48 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="Q40" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -9916,19 +9932,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -9936,37 +9952,37 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -9987,7 +10003,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9996,37 +10012,37 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -10034,10 +10050,10 @@
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -10129,7 +10145,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10138,34 +10154,34 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>66.7</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>3</v>
@@ -10271,7 +10287,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10280,25 +10296,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>57.1</v>
+        <v>63.6</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10307,21 +10323,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -10342,7 +10358,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10351,10 +10367,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -10362,26 +10378,26 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>50</v>
+        <v>90.5</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -10389,10 +10405,10 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -10689,7 +10705,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10698,25 +10714,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -11115,7 +11131,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11124,48 +11140,48 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>63.6</v>
+        <v>85</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>33.3</v>
+        <v>85.7</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -11324,7 +11340,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11333,44 +11349,48 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N62" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q62" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -11462,57 +11482,57 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>53.3</v>
+        <v>41.2</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>40</v>
+        <v>52.9</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>66.7</v>
+        <v>52.9</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -11604,46 +11624,46 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>42.9</v>
+        <v>83.3</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>57.1</v>
+        <v>33.3</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -11651,10 +11671,10 @@
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -11675,7 +11695,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11687,7 +11707,7 @@
         <v>100</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -11698,11 +11718,11 @@
         <v>100</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11746,7 +11766,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11758,22 +11778,22 @@
         <v>75</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11782,21 +11802,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -11817,19 +11837,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>33.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11837,33 +11857,37 @@
         </is>
       </c>
       <c r="I69" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q69" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -12026,34 +12050,34 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>46.7</v>
+        <v>54.5</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>60</v>
+        <v>45.5</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -12062,18 +12086,18 @@
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q72" s="4" t="n">
         <v>8</v>
@@ -12239,7 +12263,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12248,10 +12272,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -12259,14 +12283,14 @@
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -12381,7 +12405,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12390,10 +12414,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>69.2</v>
+        <v>66.7</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -12401,14 +12425,14 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>61.5</v>
+        <v>57.1</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12417,21 +12441,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -12665,57 +12689,57 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -12736,7 +12760,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12745,48 +12769,48 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>62.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -13091,7 +13115,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13100,25 +13124,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>57.6</v>
+        <v>69.2</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>45.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13127,10 +13151,10 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -13138,10 +13162,10 @@
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -13304,7 +13328,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13313,48 +13337,48 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>58.1</v>
+        <v>66.7</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>46.5</v>
+        <v>72.2</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>47.4</v>
+        <v>63.6</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>42.1</v>
+        <v>63.6</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -13517,7 +13541,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13526,10 +13550,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -13537,26 +13561,26 @@
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>58.8</v>
+        <v>45.8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>90</v>
+        <v>41.7</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -13567,7 +13591,7 @@
         <v>50</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -13659,7 +13683,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13671,22 +13695,22 @@
         <v>80</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13702,11 +13726,11 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q95" s="4" t="n">
         <v>2</v>
@@ -13730,34 +13754,34 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -14014,7 +14038,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14023,25 +14047,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>40.9</v>
+        <v>54.5</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14053,18 +14077,18 @@
         <v>50</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -14369,7 +14393,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -14378,48 +14402,48 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>55.6</v>
+        <v>64.5</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I105" s="3" t="n">
-        <v>66.7</v>
+        <v>41.9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M105" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>83</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -597,14 +597,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>39.6</v>
+        <v>41.7</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -613,21 +613,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>80</v>
+        <v>70.3</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>45</v>
+        <v>43.2</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>61</v>
+        <v>51.8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>49.2</v>
+        <v>42.9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>61.9</v>
+        <v>48.4</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>67.3</v>
+        <v>59.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1085,14 +1085,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>38.5</v>
+        <v>43.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>78.3</v>
+        <v>63.9</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>39.1</v>
+        <v>41.7</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,25 +1318,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>63.4</v>
+        <v>66.7</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40.6</v>
+        <v>40.2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>66.7</v>
+        <v>78.3</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>36.4</v>
+        <v>41.3</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,25 +1379,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>54.3</v>
+        <v>56.9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>47.6</v>
+        <v>43.1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1406,21 +1406,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>53.2</v>
+        <v>50</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>48.1</v>
+        <v>55</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>75.3</v>
+        <v>61.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>41.2</v>
+        <v>42.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>73.8</v>
+        <v>67.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>34.5</v>
+        <v>45.6</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>76.5</v>
+        <v>62.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>47.1</v>
+        <v>44.8</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,48 +2050,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>45.9</v>
+        <v>48.8</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.4</v>
+        <v>46.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>58.3</v>
+        <v>46.2</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,25 +2172,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>69</v>
+        <v>47.5</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>55.2</v>
+        <v>55.7</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>69.3</v>
+        <v>62</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>42.6</v>
+        <v>42.1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>70.7</v>
+        <v>76.3</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>43.9</v>
+        <v>44.7</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>62.5</v>
+        <v>46.6</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,37 +2610,37 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>50</v>
+        <v>46.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>53.8</v>
+        <v>55.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>50</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -2712,19 +2712,19 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63.8</v>
+        <v>46.7</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2732,37 +2732,37 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46.6</v>
+        <v>45</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>56.5</v>
+        <v>47.9</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>39.1</v>
+        <v>43.7</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2793,14 +2793,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>41.7</v>
+        <v>42.9</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>72</v>
+        <v>161</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>83.3</v>
+        <v>37.1</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="E39" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>37.5</v>
-      </c>
       <c r="H39" s="4" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>45.5</v>
+        <v>72.2</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45.5</v>
+        <v>36.1</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,48 +2965,48 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>51.9</v>
+        <v>52.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>41.2</v>
+        <v>61.5</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>61.8</v>
+        <v>53.8</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>54.5</v>
+        <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3037,26 +3037,26 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>60.4</v>
+        <v>77.8</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>73.7</v>
+        <v>57.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>47.4</v>
+        <v>57.1</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>43.1</v>
+        <v>40.9</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>73.7</v>
+        <v>62.5</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>47.4</v>
+        <v>35</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>63.3</v>
+        <v>64.3</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>46.8</v>
+        <v>45.7</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>61.5</v>
+        <v>57.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>52.5</v>
+        <v>61.3</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>38.3</v>
+        <v>40.3</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,21 +3846,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>39.5</v>
+        <v>47.8</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>60</v>
+        <v>53.4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>51.2</v>
+        <v>42.5</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>45.7</v>
+        <v>42.9</v>
       </c>
       <c r="O58" s="4" t="n">
         <v>35</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>41.9</v>
+        <v>34.2</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>64.7</v>
+        <v>69</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>52.9</v>
+        <v>38.1</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,10 +4124,10 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -4135,14 +4135,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>39.5</v>
+        <v>43.2</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>81.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>45.5</v>
+        <v>47.8</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>63.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>42.6</v>
+        <v>47.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>61.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46.2</v>
+        <v>52.8</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
@@ -4542,19 +4542,19 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>60</v>
+        <v>72.2</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4562,37 +4562,37 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,25 +4795,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>53.1</v>
+        <v>57.1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>42.9</v>
+        <v>41.4</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>59.4</v>
+        <v>52</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>81.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4928,14 +4928,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>87.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>45.9</v>
+        <v>42.4</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>42.9</v>
+        <v>41.3</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>81.2</v>
+        <v>51.9</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -5233,14 +5233,14 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -5294,14 +5294,14 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>41.4</v>
+        <v>39.2</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>69</v>
+        <v>63.6</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>44.8</v>
+        <v>39.4</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>57.9</v>
+        <v>40.4</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5355,37 +5355,37 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>42.1</v>
+        <v>45.3</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>52.6</v>
+        <v>41.7</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>36.8</v>
+        <v>45.8</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>58.3</v>
+        <v>61.6</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5538,14 +5538,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>42.9</v>
+        <v>36.6</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>63</v>
+        <v>60.4</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>44.4</v>
+        <v>39.6</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>62</v>
+        <v>59.9</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5599,14 +5599,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>42.3</v>
+        <v>46.1</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>73.3</v>
+        <v>61.5</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5649,25 +5649,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>65.8</v>
+        <v>59.2</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>43</v>
+        <v>45.6</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>55</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>62.9</v>
+        <v>55.1</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6087,14 +6087,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>41.4</v>
+        <v>45.5</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>54.5</v>
+        <v>52.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>36.4</v>
+        <v>45.9</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,25 +6137,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>52.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>41.2</v>
+        <v>43.9</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>57.4</v>
+        <v>51.6</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>38.3</v>
+        <v>48.4</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,48 +6320,48 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>38.1</v>
+        <v>35</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,25 +6381,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>53.6</v>
+        <v>53.3</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>62.7</v>
+        <v>56.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>43.4</v>
+        <v>44.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>64.7</v>
+        <v>58.1</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>55.1</v>
+        <v>47.8</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6880,14 +6880,14 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>44.9</v>
+        <v>42.9</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,10 +6896,10 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>55</v>
+        <v>43.4</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7105,25 +7105,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>90</v>
+        <v>73.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -7380,19 +7380,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>57.1</v>
+        <v>48.8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7400,14 +7400,14 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>57.1</v>
+        <v>56.1</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>57.1</v>
+        <v>46.2</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>42.9</v>
+        <v>92.3</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,25 +7460,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>44.4</v>
+        <v>52.2</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7487,14 +7487,14 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,25 +7673,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>87.5</v>
+        <v>58.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,48 +7957,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58.8</v>
+        <v>80</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>41.2</v>
+        <v>35</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>60</v>
+        <v>83.3</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8028,48 +8028,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>52.6</v>
+        <v>60</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8394,33 +8394,37 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>72.7</v>
+        <v>46.9</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q20" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -8725,7 +8729,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8734,10 +8738,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>50</v>
+        <v>75.8</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8745,37 +8749,37 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -8796,7 +8800,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8805,48 +8809,48 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G26" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="N26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -8938,7 +8942,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8947,48 +8951,48 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="G28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J28" s="4" t="n">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Q28" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q28" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -9289,7 +9293,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9298,25 +9302,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9325,21 +9329,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>33.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -9431,57 +9435,57 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="G35" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-U</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -9502,7 +9506,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9511,25 +9515,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
         <v>60</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9538,21 +9542,21 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -9573,7 +9577,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9582,10 +9586,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9596,11 +9600,11 @@
         <v>50</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9609,21 +9613,21 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
@@ -9644,7 +9648,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9653,25 +9657,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>80</v>
+        <v>58.3</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -9680,21 +9684,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -9715,7 +9719,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9724,25 +9728,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>60</v>
+        <v>59.1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9751,21 +9755,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -9857,7 +9861,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9866,48 +9870,48 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -9928,57 +9932,53 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr"/>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10079,48 +10079,48 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10505,25 +10505,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>73.7</v>
+        <v>72.2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>52.6</v>
+        <v>38.9</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10539,11 +10539,11 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q50" s="4" t="n">
         <v>5</v>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -10654,26 +10654,26 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10863,26 +10863,26 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -11065,25 +11065,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>53.3</v>
+        <v>76.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>46.7</v>
+        <v>64.7</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -11092,21 +11092,21 @@
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>44.4</v>
+        <v>85.7</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11136,48 +11136,48 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>85.7</v>
+        <v>85</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>50</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11207,25 +11207,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11633,14 +11633,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11660,18 +11660,18 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>4</v>
@@ -11695,30 +11695,34 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="J67" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11971,7 +11975,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11980,25 +11984,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>48.4</v>
+        <v>69.2</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>58.1</v>
+        <v>53.8</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -12007,21 +12011,21 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -12113,7 +12117,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12122,10 +12126,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -12133,33 +12137,37 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="N73" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="Q73" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -12322,7 +12330,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12331,25 +12339,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>77.8</v>
+        <v>70</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12358,21 +12366,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>87.5</v>
+        <v>57.1</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>62.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -12464,7 +12472,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12473,25 +12481,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>85.7</v>
+        <v>77.8</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>42.9</v>
+        <v>55.6</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -12500,21 +12508,21 @@
         </is>
       </c>
       <c r="M78" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -12535,7 +12543,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12544,10 +12552,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -12555,14 +12563,14 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12571,10 +12579,10 @@
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>77.8</v>
+        <v>57.1</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -12582,10 +12590,10 @@
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -12606,7 +12614,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12615,10 +12623,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -12626,37 +12634,37 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>70</v>
+        <v>48.7</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P80" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
@@ -12819,7 +12827,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12828,25 +12836,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>63.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>57.9</v>
+        <v>51.4</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -12855,21 +12863,21 @@
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -12890,7 +12898,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12899,10 +12907,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>68.8</v>
+        <v>59.5</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -12910,14 +12918,14 @@
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>50</v>
+        <v>40.5</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -12926,10 +12934,10 @@
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -12937,10 +12945,10 @@
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -12961,7 +12969,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12970,10 +12978,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>86.7</v>
+        <v>75</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -12981,14 +12989,14 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>46.7</v>
+        <v>41.7</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -12997,10 +13005,10 @@
         </is>
       </c>
       <c r="M85" s="3" t="n">
-        <v>100</v>
+        <v>72.2</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13016,10 @@
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
@@ -13458,7 +13466,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13467,25 +13475,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>80</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>50</v>
+        <v>44.1</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13494,21 +13502,21 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -13529,7 +13537,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13538,25 +13546,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>56.5</v>
+        <v>66.7</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>39.1</v>
+        <v>77.8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -13565,21 +13573,21 @@
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>44.4</v>
+        <v>75</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -13738,50 +13746,50 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>N-N-N-D</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="I96" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>N-N-N-N</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M96" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -13809,57 +13817,57 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>37.5</v>
+        <v>57.1</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
@@ -13951,7 +13959,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13960,48 +13968,48 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>47.4</v>
+        <v>53.1</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>42.1</v>
+        <v>46.9</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
@@ -14377,7 +14385,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -14386,10 +14394,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>68</v>
+        <v>53.1</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -14397,14 +14405,14 @@
         </is>
       </c>
       <c r="I105" s="3" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -14413,10 +14421,10 @@
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -14424,10 +14432,10 @@
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>60</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>58.1</v>
+        <v>61.9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -719,14 +719,14 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39.5</v>
+        <v>45.3</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>44.1</v>
+        <v>67.7</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>35.3</v>
+        <v>47.7</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>42</v>
+        <v>39.4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>81.8</v>
+        <v>64.7</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>36.4</v>
+        <v>47.1</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,48 +1379,48 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>56.9</v>
+        <v>48.2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>43.1</v>
+        <v>47</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
         <v>50</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>55</v>
+        <v>45.6</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>64.7</v>
+        <v>43.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45.1</v>
+        <v>43.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>60.9</v>
+        <v>46.6</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>34.8</v>
+        <v>43.1</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>43.2</v>
+        <v>42.1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>45.2</v>
+        <v>44</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>61.7</v>
+        <v>75.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45.1</v>
+        <v>37</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>42.5</v>
+        <v>41.2</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>42.1</v>
+        <v>65</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1817,26 +1817,26 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>47.4</v>
+        <v>60</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>42.9</v>
+        <v>70</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>67.7</v>
+        <v>73.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45.6</v>
+        <v>34.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>62.1</v>
+        <v>76.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>44.8</v>
+        <v>47.1</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -2102,57 +2102,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46.4</v>
+        <v>40</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-D</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>61.5</v>
-      </c>
       <c r="O27" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2294,48 +2294,48 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>53.7</v>
+        <v>55.1</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.3</v>
+        <v>41.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>47.8</v>
+        <v>52.9</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>39.1</v>
+        <v>44.1</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>65.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>42.5</v>
+        <v>40.4</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>73.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>56.7</v>
+        <v>33.3</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>46.6</v>
+        <v>62.5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,37 +2610,37 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46.6</v>
+        <v>50</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>60</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>72.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>36.1</v>
+        <v>45.7</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>66.7</v>
+        <v>47.4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>52.4</v>
+        <v>45.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>61.5</v>
+        <v>48.8</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>53.8</v>
+        <v>46.5</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>62.5</v>
+        <v>54.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3037,26 +3037,26 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-U</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="L42" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3209,37 +3209,37 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>53.7</v>
+        <v>44</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>34.1</v>
+        <v>40.9</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>54.2</v>
+        <v>42.1</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>35.4</v>
+        <v>43.9</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48.4</v>
+        <v>38.6</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>72.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>68.2</v>
+        <v>57.1</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>75</v>
+        <v>60.4</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.2</v>
+        <v>46.9</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>69.2</v>
+        <v>53.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>50</v>
+        <v>44.9</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>60.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3525,14 +3525,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>40.9</v>
+        <v>43.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>62.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>35</v>
+        <v>43.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>64.3</v>
+        <v>63.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45.7</v>
+        <v>38.3</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>57.4</v>
+        <v>64.2</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>50</v>
+        <v>37.7</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>61.3</v>
+        <v>51.8</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>40.3</v>
+        <v>43.5</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>56.5</v>
+        <v>53.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>47.8</v>
+        <v>43.2</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>53.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>42.5</v>
+        <v>46.4</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>60</v>
+        <v>63.6</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>42.9</v>
+        <v>36.4</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,25 +4185,25 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>66.7</v>
+        <v>44</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>87.5</v>
+        <v>46.2</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,25 +4246,25 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>37.3</v>
+        <v>50.7</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>72.7</v>
+        <v>61.5</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>45.5</v>
+        <v>53.8</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>47.4</v>
+        <v>42.6</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>52.8</v>
+        <v>46.2</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,25 +4795,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>57.1</v>
+        <v>53.1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>41.4</v>
+        <v>42.9</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>52</v>
+        <v>59.4</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4928,37 +4928,37 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-N</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H73" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-D</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="L73" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>43.5</v>
-      </c>
       <c r="O73" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,25 +5100,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>47.6</v>
+        <v>52.5</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,25 +5161,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>36.2</v>
+        <v>46.9</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,21 +5188,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>59.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -5294,14 +5294,14 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>39.2</v>
+        <v>41.4</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>63.6</v>
+        <v>69</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>39.4</v>
+        <v>44.8</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>40.4</v>
+        <v>43.9</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5355,26 +5355,26 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45.3</v>
+        <v>43.9</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>41.7</v>
+        <v>49.3</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>45.8</v>
+        <v>50.7</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>88.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5477,14 +5477,14 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>52.9</v>
+        <v>38.5</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5493,21 +5493,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>60</v>
+        <v>64.3</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>60</v>
+        <v>35.7</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5527,25 +5527,25 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>61.6</v>
+        <v>65.3</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>36.6</v>
+        <v>40.9</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>60.4</v>
+        <v>64.2</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>39.6</v>
+        <v>43.2</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5649,10 +5649,10 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -5660,14 +5660,14 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>45.6</v>
+        <v>46.6</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>55</v>
+        <v>64.8</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>45</v>
+        <v>42.3</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>64.7</v>
+        <v>59.6</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5782,14 +5782,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>48.5</v>
+        <v>42.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>46.4</v>
+        <v>58.3</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,25 +6015,25 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>62</v>
+        <v>55.9</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>39.2</v>
+        <v>41.6</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6042,21 +6042,21 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>63.2</v>
+        <v>59</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>47.4</v>
+        <v>46.2</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>55.1</v>
+        <v>60</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>45.5</v>
+        <v>42.2</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>52.5</v>
+        <v>60.3</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>45.9</v>
+        <v>42.5</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,25 +6137,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>43.9</v>
+        <v>41.2</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>51.6</v>
+        <v>57.4</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>48.4</v>
+        <v>38.3</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>62.3</v>
+        <v>66</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -6209,14 +6209,14 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>43.1</v>
+        <v>47.2</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6225,21 +6225,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>61</v>
+        <v>63.2</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>40.7</v>
+        <v>49.1</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>41.3</v>
+        <v>53.8</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6286,21 +6286,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>42.9</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6320,48 +6320,48 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>50</v>
+        <v>61.9</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>41.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,25 +6381,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>55.7</v>
+        <v>54.3</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>56.7</v>
+        <v>50</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>53.3</v>
+        <v>53.6</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>56.3</v>
+        <v>46.4</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6514,14 +6514,14 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>44.3</v>
+        <v>42.9</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,21 +6530,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>58.1</v>
+        <v>45.5</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>46.8</v>
+        <v>43.9</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6575,14 +6575,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>40.4</v>
+        <v>37.7</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6625,25 +6625,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>60.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>48.6</v>
+        <v>39.8</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>52.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>46</v>
+        <v>44.6</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,14 +6697,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>35.8</v>
+        <v>42.5</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>79.2</v>
+        <v>82.5</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>45.8</v>
+        <v>52.5</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6808,25 +6808,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>59.6</v>
+        <v>46.7</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7247,48 +7247,48 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>59.1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>50</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -7451,57 +7451,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>56.5</v>
+        <v>42.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8028,48 +8028,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>50</v>
+        <v>61.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>40</v>
+        <v>61.5</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -8090,57 +8090,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>75</v>
+        <v>48.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>83.3</v>
+        <v>44.4</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8170,48 +8170,48 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>83.3</v>
+        <v>44.4</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>75</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8394,37 +8394,33 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46.9</v>
+        <v>72.7</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -8516,7 +8512,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -8525,48 +8521,44 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8721,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8738,10 +8730,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>75.8</v>
+        <v>50</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8749,37 +8741,37 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -8871,19 +8863,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -8891,37 +8883,33 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr"/>
       <c r="N27" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr"/>
       <c r="Q27" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -9084,7 +9072,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9093,10 +9081,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>70</v>
+        <v>56.4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -9104,33 +9092,37 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -9222,7 +9214,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9231,10 +9223,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>61.5</v>
+        <v>68.8</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -9242,14 +9234,14 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9258,21 +9250,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -9435,19 +9427,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -9455,26 +9447,26 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -9482,10 +9474,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -9719,7 +9711,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9728,25 +9720,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>59.1</v>
+        <v>73.3</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9755,21 +9747,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>62.5</v>
+        <v>85.7</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -9861,46 +9853,46 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -9908,10 +9900,10 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -9932,53 +9924,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>D-U-N-U</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n">
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>D-U-N-N</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -10141,7 +10137,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10150,48 +10146,48 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>43.8</v>
+        <v>40.6</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -10283,7 +10279,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10292,10 +10288,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -10303,14 +10299,14 @@
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10319,21 +10315,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -10354,7 +10350,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10363,25 +10359,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>81.2</v>
+        <v>68.3</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>37.5</v>
+        <v>51.2</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10390,21 +10386,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -10496,7 +10492,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10505,25 +10501,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>72.2</v>
+        <v>69.2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10532,21 +10528,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -10634,7 +10630,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10643,10 +10639,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>68</v>
+        <v>73.7</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -10654,37 +10650,37 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>42.9</v>
+        <v>80</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>40</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -10843,7 +10839,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10852,48 +10848,48 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>66.7</v>
+        <v>37.1</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -11056,19 +11052,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>76.5</v>
+        <v>66.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -11076,14 +11072,14 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>64.7</v>
+        <v>66.7</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -11092,10 +11088,10 @@
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -11103,10 +11099,10 @@
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -11269,57 +11265,49 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>50</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr"/>
       <c r="Q61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -11340,7 +11328,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11349,37 +11337,37 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>69.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M62" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -11387,10 +11375,10 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -11624,7 +11612,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11633,14 +11621,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
@@ -11651,7 +11639,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11660,18 +11648,18 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
         <v>4</v>
@@ -11975,7 +11963,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11984,25 +11972,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>69.2</v>
+        <v>48.4</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>53.8</v>
+        <v>58.1</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -12011,21 +11999,21 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -12117,7 +12105,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12126,10 +12114,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>68.8</v>
+        <v>100</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -12137,37 +12125,33 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>83.3</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr"/>
       <c r="Q73" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -12330,7 +12314,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12339,25 +12323,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12366,21 +12350,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>57.1</v>
+        <v>46.7</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -12401,7 +12385,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12410,10 +12394,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>53.8</v>
+        <v>60.9</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -12421,14 +12405,14 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>46.2</v>
+        <v>56.5</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12448,7 +12432,7 @@
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q77" s="4" t="n">
         <v>5</v>
@@ -12543,7 +12527,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12552,10 +12536,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -12563,14 +12547,14 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12579,10 +12563,10 @@
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>57.1</v>
+        <v>77.8</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -12590,10 +12574,10 @@
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -12614,19 +12598,19 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -12634,26 +12618,26 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>43.8</v>
+        <v>55.6</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -12661,10 +12645,10 @@
         </is>
       </c>
       <c r="P80" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -12756,57 +12740,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -12827,7 +12811,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12836,25 +12820,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>51.4</v>
+        <v>40.5</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -12863,21 +12847,21 @@
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
@@ -12969,7 +12953,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12978,10 +12962,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -12989,14 +12973,14 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>41.7</v>
+        <v>48.7</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -13005,21 +12989,21 @@
         </is>
       </c>
       <c r="M85" s="3" t="n">
-        <v>72.2</v>
+        <v>53.3</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>44.4</v>
+        <v>46.7</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -13111,7 +13095,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13120,48 +13104,44 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-D</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>37.5</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr"/>
       <c r="Q87" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -13395,7 +13375,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13404,25 +13384,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>35.3</v>
+        <v>44.4</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -13431,10 +13411,10 @@
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -13442,10 +13422,10 @@
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -13466,7 +13446,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13475,25 +13455,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>44.1</v>
+        <v>45.7</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13502,10 +13482,10 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>72.7</v>
+        <v>46.7</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -13513,10 +13493,10 @@
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>45.5</v>
+        <v>46.7</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -13537,7 +13517,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13546,48 +13526,48 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="N93" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="J93" s="4" t="n">
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="Q93" s="4" t="n">
         <v>9</v>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -13608,7 +13588,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13617,10 +13597,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>65.2</v>
+        <v>80.8</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13628,14 +13608,14 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>47.8</v>
+        <v>42.3</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -13644,21 +13624,21 @@
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>54.5</v>
+        <v>69.2</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>63.6</v>
+        <v>46.2</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -13679,7 +13659,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13688,44 +13668,48 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N95" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q95" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -13746,50 +13730,50 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N96" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
@@ -13817,57 +13801,57 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -13959,7 +13943,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13968,48 +13952,48 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>53.1</v>
+        <v>57.1</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>46.9</v>
+        <v>37.1</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>37.5</v>
+        <v>43.8</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100">
@@ -14030,7 +14014,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14039,25 +14023,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>87.5</v>
+        <v>61.5</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14066,10 +14050,10 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -14077,10 +14061,10 @@
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -14101,7 +14085,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -14110,25 +14094,25 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>72.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>41.7</v>
+        <v>45.5</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
@@ -14137,21 +14121,21 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>58.3</v>
+        <v>81.8</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>41.7</v>
+        <v>45.5</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
@@ -14172,7 +14156,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14181,25 +14165,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-U</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14211,18 +14195,18 @@
         <v>100</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -14314,7 +14298,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -14323,25 +14307,25 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>67.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>45.2</v>
+        <v>42.3</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -14350,21 +14334,21 @@
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,25 +647,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56.6</v>
+        <v>61.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>43.4</v>
+        <v>47.7</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>56.2</v>
+        <v>65.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>58.1</v>
+        <v>55.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39.5</v>
+        <v>42.1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>59.1</v>
+        <v>69.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>59.1</v>
+        <v>47.6</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>59</v>
+        <v>54.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.4</v>
+        <v>40.6</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>60.9</v>
+        <v>50.7</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>47.8</v>
+        <v>38.4</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,25 +891,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>69.8</v>
+        <v>57.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>76.2</v>
+        <v>68.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>76.2</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -963,14 +963,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>47.6</v>
+        <v>40</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>6</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>54.7</v>
+        <v>66.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1146,14 +1146,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43.2</v>
+        <v>40.4</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>42.7</v>
+        <v>40.5</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,48 +1257,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>55.9</v>
+        <v>66.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,48 +1440,48 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>64.7</v>
+        <v>44.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45.1</v>
+        <v>43</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>52.2</v>
+        <v>45.7</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>70.7</v>
+        <v>62.9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.7</v>
+        <v>43.2</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>69.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>33.3</v>
+        <v>40.9</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>54</v>
+        <v>36.6</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>75</v>
+        <v>76.7</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>75</v>
+        <v>43.3</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,48 +1745,48 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-D</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="L21" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-U</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>46</v>
-      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>52.2</v>
+        <v>43.9</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -1797,57 +1797,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>61.1</v>
+        <v>84.2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>50</v>
+        <v>73.7</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>55.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>55.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,25 +1989,25 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>39.7</v>
+        <v>48.6</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>39.3</v>
+        <v>55.2</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,25 +2172,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>60.8</v>
+        <v>72.5</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>47.5</v>
+        <v>42</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>58.4</v>
+        <v>77.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>51.9</v>
+        <v>38.9</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2233,37 +2233,37 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>28</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>53.6</v>
+        <v>60.7</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>28</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>60</v>
+        <v>43.8</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>70</v>
+        <v>56.2</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2294,25 +2294,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>53.7</v>
+        <v>50.9</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>43.3</v>
+        <v>40</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>62.5</v>
+        <v>45.7</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>43.8</v>
+        <v>42.9</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>85.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.9</v>
+        <v>55.9</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>90</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59.4</v>
+        <v>60.9</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>46.9</v>
+        <v>56.2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>45.7</v>
+        <v>58.3</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,25 +2660,25 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>60</v>
+        <v>56.9</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>43.3</v>
+        <v>45.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>68.8</v>
+        <v>63</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>43.8</v>
+        <v>51.9</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>63.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>45.8</v>
+        <v>43.7</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>77.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>44.4</v>
+        <v>49.4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>42.9</v>
+        <v>51.3</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,25 +2965,25 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>42.1</v>
+        <v>47.2</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>36.8</v>
+        <v>48.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>36.4</v>
+        <v>52.4</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>83.3</v>
+        <v>37.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3037,37 +3037,37 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>58.3</v>
+        <v>62.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>53.8</v>
+        <v>47.4</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3175,21 +3175,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -3261,46 +3261,46 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>47.8</v>
+        <v>64.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>44.6</v>
+        <v>59.4</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>39.3</v>
+        <v>43.8</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,25 +3392,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>75</v>
+        <v>57.6</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.2</v>
+        <v>37.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>69.2</v>
+        <v>56.6</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>50</v>
+        <v>39.5</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>67.5</v>
+        <v>52.4</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3464,14 +3464,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45.5</v>
+        <v>49</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>57.1</v>
+        <v>44.1</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>51.4</v>
+        <v>59.3</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>80</v>
+        <v>48.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>60</v>
+        <v>55.2</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>83.3</v>
+        <v>54.5</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>66.7</v>
+        <v>45.5</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>68.8</v>
+        <v>60.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4013,14 +4013,14 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>43.8</v>
+        <v>57.6</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>85.7</v>
+        <v>69.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>70.3</v>
+        <v>62.6</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45.1</v>
+        <v>40.7</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>64.3</v>
+        <v>60.8</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>52.9</v>
+        <v>43.2</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>64.3</v>
+        <v>62.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>73.3</v>
+        <v>52.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46.7</v>
+        <v>42.6</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>53.8</v>
+        <v>44.2</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,25 +4368,25 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>49.2</v>
+        <v>42.6</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>43.7</v>
+        <v>47</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>47.7</v>
+        <v>46.2</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>44.2</v>
+        <v>40</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,48 +4429,48 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>80.3</v>
+        <v>58.8</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N65" s="3" t="n">
-        <v>47.4</v>
+        <v>42.9</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>76.8</v>
+        <v>59</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>83.3</v>
+        <v>65.2</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,48 +4673,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E69" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="O69" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>52.9</v>
+        <v>51.6</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4867,37 +4867,37 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>50</v>
+        <v>62.2</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,48 +4917,48 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>47.6</v>
+        <v>48.9</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>45.9</v>
+        <v>42.4</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>70.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>45.8</v>
+        <v>52.5</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,48 +5161,48 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>59.7</v>
+        <v>62.3</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-N</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G77" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-U</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N77" s="3" t="n">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5588,25 +5588,25 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>70.7</v>
+        <v>62.3</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>71</v>
+        <v>62.7</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>45.2</v>
+        <v>56.9</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>47.7</v>
+        <v>54.2</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,14 +5904,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>51.1</v>
+        <v>45.8</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>59</v>
+        <v>46.2</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5965,26 +5965,26 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>44.4</v>
+        <v>46.2</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>39.1</v>
+        <v>54.5</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>47.8</v>
+        <v>45.5</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,48 +6015,48 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>41.3</v>
+        <v>39.2</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>150</v>
+        <v>79</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>44.8</v>
+        <v>55.2</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>50.7</v>
+        <v>34.5</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>62.9</v>
+        <v>55.1</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -6087,14 +6087,14 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>41.4</v>
+        <v>45.5</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>68.8</v>
+        <v>56.6</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,25 +6137,25 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>49.4</v>
+        <v>64</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.8</v>
+        <v>44</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>60.7</v>
+        <v>63.6</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,25 +6381,25 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>41.8</v>
+        <v>34.7</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>76.5</v>
+        <v>72.2</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>64.2</v>
+        <v>57.4</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>43.4</v>
+        <v>57.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>47.4</v>
+        <v>57.7</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>54.9</v>
+        <v>54.4</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6880,14 +6880,14 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>51.2</v>
+        <v>43.1</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,21 +6896,21 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
-        <v>63</v>
+        <v>58.2</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N105" s="3" t="n">
-        <v>55.6</v>
+        <v>39.2</v>
       </c>
       <c r="O105" s="4" t="n">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -7176,48 +7176,48 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>63.6</v>
+        <v>61.9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>45.5</v>
+        <v>47.6</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7247,25 +7247,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7389,25 +7389,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46.7</v>
+        <v>41.2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>69.2</v>
+        <v>61.9</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>46.2</v>
+        <v>38.1</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7471,14 +7471,14 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7487,21 +7487,21 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7531,44 +7531,48 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7731,7 +7735,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7740,10 +7744,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>56.5</v>
+        <v>42.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7751,19 +7755,19 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
@@ -7774,11 +7778,11 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>6</v>
@@ -7873,7 +7877,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7882,25 +7886,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-N</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7909,21 +7913,21 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -8086,46 +8090,46 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -8133,10 +8137,10 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -8228,7 +8232,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8237,10 +8241,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>64.7</v>
+        <v>57.1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -8248,37 +8252,37 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>41.2</v>
+        <v>42.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -8370,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8379,25 +8383,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8409,18 +8413,18 @@
         <v>100</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -8441,7 +8445,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8450,25 +8454,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>41.4</v>
+        <v>51.4</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -8477,21 +8481,21 @@
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>75</v>
+        <v>53.3</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -8512,57 +8516,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -8725,7 +8729,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8734,41 +8738,41 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-U</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
@@ -8930,7 +8934,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8939,25 +8943,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>70.8</v>
+        <v>56.2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>54.2</v>
+        <v>56.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -8966,21 +8970,21 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -9001,7 +9005,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -9010,48 +9014,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="N29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I29" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P29" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -9072,7 +9076,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -9081,25 +9085,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46.7</v>
+        <v>51.1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
         <v>40</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -9108,21 +9112,21 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>37.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -9143,7 +9147,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9152,25 +9156,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>83.3</v>
+        <v>77.8</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -9179,10 +9183,10 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -9190,10 +9194,10 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -9285,7 +9289,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9294,10 +9298,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>47.8</v>
+        <v>60</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -9305,14 +9309,14 @@
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -9321,21 +9325,21 @@
         </is>
       </c>
       <c r="M33" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="N33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q33" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -9498,53 +9502,57 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
         <v>50</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>66.7</v>
+      </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q36" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -9636,7 +9644,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9645,10 +9653,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -9656,37 +9664,37 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>51.9</v>
+        <v>66.7</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>40</v>
+        <v>83.3</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -9778,7 +9786,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9787,10 +9795,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>80</v>
+        <v>52.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9798,14 +9806,14 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -9814,21 +9822,21 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -9849,57 +9857,57 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J41" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>75</v>
-      </c>
       <c r="Q41" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -9920,57 +9928,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>U-N-U-N</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>U-N-U-U</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="N42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -10062,19 +10070,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -10082,19 +10090,19 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
@@ -10105,7 +10113,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
@@ -10204,19 +10212,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -10224,37 +10232,37 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46.7</v>
+        <v>37.5</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -10346,7 +10354,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10355,25 +10363,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>80</v>
+        <v>62.2</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>40</v>
+        <v>48.6</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10382,21 +10390,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -10417,57 +10425,57 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>73.3</v>
+        <v>53.3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>42.9</v>
+        <v>61.1</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -10559,53 +10567,57 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="N51" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="Q51" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -11052,57 +11064,53 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr"/>
       <c r="Q58" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -11123,7 +11131,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11139,18 +11147,18 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11159,10 +11167,10 @@
         </is>
       </c>
       <c r="M59" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -11170,10 +11178,10 @@
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -11194,7 +11202,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11203,25 +11211,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>64.3</v>
+        <v>40.6</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11230,21 +11238,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -11332,7 +11340,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11341,10 +11349,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>63.6</v>
+        <v>60.7</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11352,14 +11360,14 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11368,10 +11376,10 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -11379,10 +11387,10 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -11474,7 +11482,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11483,48 +11491,48 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>44</v>
+        <v>48.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>52</v>
+        <v>53.5</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>58.3</v>
+        <v>47.1</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>58.3</v>
+        <v>52.9</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -11545,7 +11553,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11554,48 +11562,48 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>85.7</v>
+        <v>59.5</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P65" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -11616,57 +11624,57 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>72.7</v>
+        <v>52.9</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>45.5</v>
+        <v>52.9</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -11825,7 +11833,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -11834,48 +11842,48 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
         <v>60</v>
       </c>
       <c r="J69" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N69" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P69" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -12038,19 +12046,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -12058,37 +12066,37 @@
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P72" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -12109,7 +12117,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12118,44 +12126,48 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -12318,7 +12330,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12327,48 +12339,48 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>53.3</v>
+        <v>58.1</v>
       </c>
       <c r="G76" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="N76" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="n">
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="n">
         <v>46.7</v>
       </c>
-      <c r="J76" s="4" t="n">
+      <c r="Q76" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q76" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -12389,46 +12401,46 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>57.1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>61.5</v>
+        <v>66.7</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -12436,10 +12448,10 @@
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>53.8</v>
+        <v>66.7</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -12886,7 +12898,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12895,37 +12907,37 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>66.7</v>
+        <v>46.9</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>52.4</v>
+        <v>53.1</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -12933,10 +12945,10 @@
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
@@ -13237,57 +13249,57 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -13308,19 +13320,19 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13328,19 +13340,19 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
@@ -13351,7 +13363,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -13379,19 +13391,19 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>56.5</v>
+        <v>84.2</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -13399,37 +13411,37 @@
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>39.1</v>
+        <v>47.4</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M91" s="3" t="n">
-        <v>58.3</v>
+        <v>87.5</v>
       </c>
       <c r="N91" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -13450,19 +13462,19 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>58.3</v>
+        <v>44.4</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13470,14 +13482,14 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13486,10 +13498,10 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>60</v>
+        <v>52.9</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -13497,10 +13509,10 @@
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>60</v>
+        <v>52.9</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93">
@@ -13521,46 +13533,46 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>55.2</v>
+        <v>55.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>48.3</v>
+        <v>77.8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -13568,10 +13580,10 @@
         </is>
       </c>
       <c r="P93" s="3" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
@@ -13805,7 +13817,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13814,48 +13826,48 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="G97" s="4" t="n">
         <v>19</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>52.6</v>
+        <v>47.4</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -14018,57 +14030,57 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>40</v>
+        <v>73.3</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>33.3</v>
+        <v>83.3</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -14373,7 +14385,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -14382,25 +14394,25 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="G105" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>44.4</v>
-      </c>
       <c r="J105" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -14409,10 +14421,10 @@
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -14420,10 +14432,10 @@
         </is>
       </c>
       <c r="P105" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>55.3</v>
+        <v>58.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>42.1</v>
+        <v>39.5</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>69.8</v>
+        <v>59.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>47.6</v>
+        <v>59.1</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>54.1</v>
+        <v>74</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>40.6</v>
+        <v>38.4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>50.7</v>
+        <v>75</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>38.4</v>
+        <v>39.3</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1074,48 +1074,48 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>67.5</v>
+        <v>57.8</v>
       </c>
       <c r="E10" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-U</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-N</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>72.2</v>
-      </c>
       <c r="L10" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>44.4</v>
+        <v>56</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>66.3</v>
+        <v>55.6</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>40.4</v>
+        <v>44.4</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>59.5</v>
+        <v>57</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>40.5</v>
+        <v>46.8</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,48 +1257,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.7</v>
+        <v>55.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.4</v>
+        <v>47.1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,25 +1318,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>66.3</v>
+        <v>64.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36</v>
+        <v>37.3</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>34.3</v>
+        <v>39.6</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60.6</v>
+        <v>55.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>48.5</v>
+        <v>46.4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>56.2</v>
+        <v>54.8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>56.2</v>
+        <v>48.4</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>36.6</v>
+        <v>54</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>76.7</v>
+        <v>75</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>43.3</v>
+        <v>75</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -1797,57 +1797,57 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>84.2</v>
+        <v>61.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>73.7</v>
+        <v>50</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2050,48 +2050,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>45.9</v>
+        <v>44.6</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.4</v>
+        <v>41.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>45</v>
+        <v>43.1</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>45</v>
+        <v>46.6</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2172,48 +2172,48 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>72.5</v>
+        <v>58.4</v>
       </c>
       <c r="E28" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="L28" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="O28" s="4" t="n">
         <v>69</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="O28" s="4" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,25 +2477,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>60.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>56.2</v>
+        <v>42.7</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2507,18 +2507,18 @@
         <v>66.7</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>58.3</v>
+        <v>45.1</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>63.8</v>
+        <v>54</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2732,14 +2732,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46.6</v>
+        <v>43.1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>63.2</v>
+        <v>54.1</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>49.4</v>
+        <v>44.4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>51.3</v>
+        <v>42.9</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>37.5</v>
+        <v>83.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3037,37 +3037,37 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>62.5</v>
+        <v>58.3</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3159,26 +3159,26 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>47.4</v>
+        <v>57.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3261,46 +3261,46 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>64.2</v>
+        <v>47.8</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>59.4</v>
+        <v>44.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>43.8</v>
+        <v>39.3</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>48.3</v>
+        <v>80</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>55.2</v>
+        <v>60</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>54.5</v>
+        <v>83.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3758,48 +3758,48 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>51.5</v>
+        <v>44.9</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N54" s="3" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>60.8</v>
+        <v>64.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>43.2</v>
+        <v>52.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>62.5</v>
+        <v>64.3</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>50</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,25 +5100,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57.6</v>
+        <v>58.7</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>52.5</v>
+        <v>43.9</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,25 +5161,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>62.3</v>
+        <v>59.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>36.2</v>
+        <v>46.5</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>47.4</v>
+        <v>46.9</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>53.3</v>
+        <v>39.1</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5493,18 +5493,18 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="O82" s="4" t="n">
         <v>8</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>54.2</v>
+        <v>47.7</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,14 +5904,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45.8</v>
+        <v>51.1</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>46.2</v>
+        <v>48.7</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>46.2</v>
+        <v>59</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5965,26 +5965,26 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>54.5</v>
+        <v>39.1</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>45.5</v>
+        <v>47.8</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>62.7</v>
+        <v>46.7</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6530,21 +6530,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>57.4</v>
+        <v>64.2</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>57.4</v>
+        <v>43.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>50</v>
+        <v>57.9</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>57.7</v>
+        <v>47.4</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7247,25 +7247,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>53.8</v>
+        <v>61.5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -7274,21 +7274,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7389,25 +7389,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>61.8</v>
+        <v>72.7</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>41.2</v>
+        <v>36.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>61.9</v>
+        <v>60</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>38.1</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>56.2</v>
+        <v>72.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7684,14 +7684,14 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7744,37 +7744,37 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>42.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50</v>
+        <v>58.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>50</v>
+        <v>69.2</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7886,25 +7886,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7913,21 +7913,21 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,48 +7957,48 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>42.9</v>
+        <v>58.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>D/N/U</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>33.3</v>
-      </c>
       <c r="N14" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8312,25 +8312,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>66.7</v>
+        <v>37</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,25 +8383,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>55.6</v>
+        <v>37.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8413,18 +8413,18 @@
         <v>100</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -8516,57 +8516,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -8800,57 +8800,57 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>63.6</v>
+        <v>40</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.7</v>
+        <v>52</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>60</v>
+        <v>58.3</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>56.2</v>
+        <v>51.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -8954,37 +8954,37 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>56.2</v>
+        <v>55.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>33.3</v>
+        <v>53.8</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9298,48 +9298,48 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>60</v>
+        <v>56.5</v>
       </c>
       <c r="G33" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-U</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J33" s="4" t="n">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q33" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>72.7</v>
+        <v>51.7</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -9593,14 +9593,14 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>63.6</v>
+        <v>44.8</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -9609,10 +9609,10 @@
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>75</v>
+        <v>64.3</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -9795,10 +9795,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>52.4</v>
+        <v>80</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -9806,14 +9806,14 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -9822,21 +9822,21 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -9928,57 +9928,57 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -10070,39 +10070,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
@@ -10212,19 +10212,19 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -10232,37 +10232,37 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>37.5</v>
+        <v>46.7</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -10567,57 +10567,53 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>75</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr"/>
       <c r="Q51" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -10780,7 +10776,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10789,10 +10785,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>52.4</v>
+        <v>54.1</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -10800,14 +10796,14 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>52.4</v>
+        <v>59.5</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -10816,21 +10812,21 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -11202,7 +11198,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11211,25 +11207,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>68.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>40.6</v>
+        <v>64.3</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>N-D-U-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -11238,21 +11234,21 @@
         </is>
       </c>
       <c r="M60" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q60" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -12330,7 +12326,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12339,10 +12335,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>58.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -12350,14 +12346,14 @@
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>51.6</v>
+        <v>46.2</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12366,21 +12362,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>73.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>46.7</v>
+        <v>35.7</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
@@ -12401,46 +12397,46 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
         <v>57.1</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -12448,10 +12444,10 @@
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>66.7</v>
+        <v>53.8</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -12756,57 +12752,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -13249,57 +13245,57 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>40</v>
+        <v>58.3</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -13320,19 +13316,19 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13340,19 +13336,19 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M90" s="3" t="n">
@@ -13363,7 +13359,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
@@ -13959,19 +13955,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>60</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -13979,26 +13975,26 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>60</v>
+        <v>46.9</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -14006,10 +14002,10 @@
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
@@ -14030,57 +14026,57 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>73.3</v>
+        <v>40</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>39.7</v>
+        <v>45.3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>63</v>
+        <v>66.2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>37</v>
+        <v>41.2</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,48 +1196,48 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>76.5</v>
+        <v>49.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N12" s="3" t="n">
-        <v>60</v>
+        <v>48.6</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1318,25 +1318,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>78.7</v>
+        <v>66.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>42.6</v>
+        <v>36.4</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,48 +1440,48 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>64.7</v>
+        <v>44.6</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45.1</v>
+        <v>43.4</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>52.2</v>
+        <v>46.5</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2355,25 +2355,25 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.9</v>
+        <v>54.3</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,48 +2477,48 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59.6</v>
+        <v>71</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-N</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-U</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N33" s="3" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,30 +2599,30 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-U</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>D</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-D</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,48 +2965,48 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>53.4</v>
+        <v>42.1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46.6</v>
+        <v>36.8</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>48.1</v>
+        <v>40</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>48.1</v>
+        <v>40</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -3017,57 +3017,57 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>44</v>
+        <v>54.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>44</v>
+        <v>45.5</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3139,57 +3139,57 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3200,57 +3200,57 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60.5</v>
+        <v>50.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>46.5</v>
+        <v>47.8</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>62.5</v>
+        <v>47.8</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>56.2</v>
+        <v>50.7</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>53.8</v>
+        <v>47.6</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3880,48 +3880,48 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.5</v>
+        <v>58.7</v>
       </c>
       <c r="E56" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L56" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H56" s="4" t="n">
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="O56" s="4" t="n">
         <v>16</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>73</v>
+        <v>48.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3952,26 +3952,26 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>40.5</v>
+        <v>41.7</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>70</v>
+        <v>47.5</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>43.3</v>
+        <v>42.4</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>37.1</v>
+        <v>37.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>37.8</v>
+        <v>46.2</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>44.2</v>
+        <v>44.9</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>71.8</v>
+        <v>65.5</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4490,25 +4490,25 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>35.8</v>
+        <v>48.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>50</v>
+        <v>65.7</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>45</v>
+        <v>37.1</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>61</v>
+        <v>49.1</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4806,26 +4806,26 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>65.7</v>
+        <v>45.5</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>45.7</v>
+        <v>39.4</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4928,14 +4928,14 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>43.5</v>
+        <v>55.6</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4978,25 +4978,25 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>56.9</v>
+        <v>54.4</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>38.5</v>
+        <v>46.7</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5005,21 +5005,21 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>50</v>
+        <v>45.3</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>50</v>
+        <v>45.3</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5111,14 +5111,14 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>42.4</v>
+        <v>45.9</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>52.5</v>
+        <v>45.8</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5161,25 +5161,25 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>62.3</v>
+        <v>61.8</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>36.2</v>
+        <v>40.1</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,21 +5188,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>63.2</v>
+        <v>58.3</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>47.4</v>
+        <v>41.7</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>66.7</v>
+        <v>65.5</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>34.6</v>
+        <v>45.5</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>35.7</v>
+        <v>52.9</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>63.2</v>
+        <v>65.8</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5416,14 +5416,14 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>42.4</v>
+        <v>43.4</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>36</v>
+        <v>56.5</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,37 +5466,37 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>57.7</v>
+        <v>42.5</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5649,25 +5649,25 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>61.5</v>
+        <v>61.2</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>42.3</v>
+        <v>43.3</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,25 +6564,25 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>61.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>43.5</v>
+        <v>40</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,14 +6697,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>35.8</v>
+        <v>42.1</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>35.5</v>
+        <v>50</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7460,25 +7460,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>66.7</v>
+        <v>82.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>33.3</v>
+        <v>37.9</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,48 +7815,48 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="G12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-N</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7957,25 +7957,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>62.1</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>37.9</v>
+        <v>35</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7984,21 +7984,21 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>62.5</v>
+        <v>77.8</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>37.5</v>
+        <v>44.4</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -8090,34 +8090,34 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>57.1</v>
+        <v>34.6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8129,18 +8129,18 @@
         <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -9152,44 +9152,48 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q31" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -9281,7 +9285,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9290,37 +9294,37 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>69.7</v>
+        <v>76.2</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>48.5</v>
+        <v>61.9</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -9328,10 +9332,10 @@
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -9423,34 +9427,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9854,25 +9854,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>56.2</v>
+        <v>100</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>56.2</v>
+        <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -9916,30 +9916,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -10050,49 +10054,57 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="G44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="J44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -10113,19 +10125,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>75</v>
+        <v>61.5</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -10133,26 +10145,26 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -10160,10 +10172,10 @@
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -10255,7 +10267,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10264,25 +10276,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -10291,21 +10303,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -10890,53 +10902,57 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="N56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="inlineStr"/>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -10957,7 +10973,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10966,48 +10982,48 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>52</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>36.8</v>
+        <v>48</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -11170,7 +11186,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11179,48 +11195,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>42.1</v>
+        <v>46.2</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -11525,7 +11541,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11534,48 +11550,48 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>72.7</v>
+        <v>69</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P65" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
@@ -11596,7 +11612,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11605,25 +11621,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>38.5</v>
+        <v>53.3</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -11632,21 +11648,21 @@
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -11951,7 +11967,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -11960,10 +11976,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>75</v>
+        <v>59.4</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -11971,14 +11987,14 @@
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>50</v>
+        <v>56.2</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -11987,10 +12003,10 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>85.7</v>
+        <v>46.2</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -11998,10 +12014,10 @@
         </is>
       </c>
       <c r="P71" s="3" t="n">
-        <v>57.1</v>
+        <v>46.2</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -12093,57 +12109,53 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="n">
-        <v>80</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n">
-        <v>60</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr"/>
       <c r="Q73" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -12164,7 +12176,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12173,48 +12185,48 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="I74" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="P74" s="3" t="n">
-        <v>40</v>
+        <v>36.4</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -12306,7 +12318,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12315,25 +12327,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>51.9</v>
+        <v>85.7</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>37</v>
+        <v>61.9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12342,21 +12354,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -12377,7 +12389,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12386,10 +12398,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -12397,26 +12409,26 @@
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>38.5</v>
+        <v>44</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -12427,7 +12439,7 @@
         <v>50</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -12519,7 +12531,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12528,25 +12540,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12555,21 +12567,21 @@
         </is>
       </c>
       <c r="M79" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -12661,7 +12673,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12670,25 +12682,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63</v>
+        <v>66.7</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12697,10 +12709,10 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -12708,10 +12720,10 @@
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>45.5</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -12732,53 +12744,57 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-U</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="P82" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="Q82" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-N</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="inlineStr"/>
-      <c r="Q82" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -12941,7 +12957,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -12950,10 +12966,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>73.3</v>
+        <v>69.2</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -12961,14 +12977,14 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>53.3</v>
+        <v>48.7</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -12977,21 +12993,21 @@
         </is>
       </c>
       <c r="M85" s="3" t="n">
-        <v>80</v>
+        <v>57.9</v>
       </c>
       <c r="N85" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P85" s="3" t="n">
-        <v>40</v>
+        <v>52.6</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
@@ -14006,7 +14022,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14015,25 +14031,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>42.9</v>
+        <v>81.8</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>35.7</v>
+        <v>54.5</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14042,21 +14058,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -14148,7 +14164,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14157,48 +14173,48 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>87</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>39.1</v>
+        <v>43.5</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66.7</v>
+        <v>83</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>40.7</v>
+        <v>39.6</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -613,21 +613,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>61.3</v>
+        <v>65.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>58.8</v>
+        <v>68.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>47.1</v>
+        <v>40.9</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>57.4</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44.7</v>
+        <v>48.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>56.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>43.7</v>
+        <v>38.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>57.1</v>
+        <v>64.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>60</v>
+        <v>41.2</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>76.5</v>
+        <v>63.6</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1207,14 +1207,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>58.8</v>
+        <v>43.9</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>77.8</v>
+        <v>58.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>77.8</v>
+        <v>55.6</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>65.5</v>
+        <v>52.8</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>75</v>
+        <v>52.9</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>62.5</v>
+        <v>52.9</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>47.9</v>
+        <v>58</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1390,37 +1390,37 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>43.7</v>
+        <v>39.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>56.7</v>
+        <v>57.5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>40</v>
+        <v>45.2</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1440,25 +1440,25 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>48.1</v>
+        <v>58.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>43.4</v>
+        <v>39.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>49.2</v>
+        <v>62.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>70.7</v>
+        <v>62.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1573,14 +1573,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>34.7</v>
+        <v>43.6</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>69.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>33.3</v>
+        <v>42.2</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>42.3</v>
+        <v>62.1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>72.2</v>
+        <v>54.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1745,25 +1745,25 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>63.5</v>
+        <v>56.8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>36.5</v>
+        <v>42.4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>52.8</v>
+        <v>38.9</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1939,14 +1939,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>43.8</v>
+        <v>45.7</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>42.1</v>
+        <v>46.2</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>63.5</v>
+        <v>69.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>41.7</v>
+        <v>42.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>58.6</v>
+        <v>70.7</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>41.4</v>
+        <v>43.9</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -2590,34 +2590,34 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>62.5</v>
+        <v>53.8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>87.5</v>
+        <v>46.2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>59.4</v>
+        <v>42.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,14 +2854,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40</v>
+        <v>48.5</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>55</v>
+        <v>45.9</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>40</v>
+        <v>51.4</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3327,25 +3327,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>56.1</v>
+        <v>53.9</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40.8</v>
+        <v>46.7</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>57.1</v>
+        <v>71</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>47.6</v>
+        <v>45.2</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3399,14 +3399,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>43.2</v>
+        <v>34.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3449,25 +3449,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>57.5</v>
+        <v>73.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46.2</v>
+        <v>39</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3476,21 +3476,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>54.3</v>
+        <v>52.9</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>48.6</v>
+        <v>35.3</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3754,25 +3754,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>70.3</v>
+        <v>49.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>43.2</v>
+        <v>49.1</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>83.3</v>
+        <v>45.8</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>44.4</v>
+        <v>54.2</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>66</v>
+        <v>46.4</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3887,14 +3887,14 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>50</v>
+        <v>48.2</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3903,21 +3903,21 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>68.2</v>
+        <v>52.4</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>59.1</v>
+        <v>47.6</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3937,25 +3937,25 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>47.2</v>
+        <v>42</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>66.7</v>
+        <v>63.1</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>57.1</v>
+        <v>43.1</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>72.2</v>
+        <v>61</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -4009,14 +4009,14 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>60</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4181,25 +4181,25 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45.8</v>
+        <v>40</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4208,21 +4208,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>59.1</v>
+        <v>44.9</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>39.4</v>
+        <v>49.2</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>59.3</v>
+        <v>46</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>48.1</v>
+        <v>44.8</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>45.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4497,14 +4497,14 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>44.9</v>
+        <v>42.4</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>50.8</v>
+        <v>69.2</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>47.5</v>
+        <v>38.5</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -4538,57 +4538,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>52.6</v>
+        <v>41.7</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>62.5</v>
+        <v>33.3</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>55.6</v>
+        <v>63.2</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4619,14 +4619,14 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>44.4</v>
+        <v>47.4</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>52.4</v>
+        <v>62.5</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>47.6</v>
+        <v>37.5</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4924,26 +4924,26 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>47.6</v>
+        <v>40.6</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>66.2</v>
+        <v>54.5</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4985,14 +4985,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>40</v>
+        <v>43.7</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>42.9</v>
+        <v>43.6</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>69.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5046,14 +5046,14 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>53.5</v>
+        <v>48.3</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>57.9</v>
+        <v>45.5</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5096,25 +5096,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>41.9</v>
+        <v>39.7</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>41</v>
+        <v>55.4</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>65</v>
+        <v>57.8</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>35</v>
+        <v>48.4</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5611,18 +5611,18 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>63</v>
+        <v>59.3</v>
       </c>
       <c r="L84" s="4" t="n">
         <v>27</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>37</v>
+        <v>55.6</v>
       </c>
       <c r="O84" s="4" t="n">
         <v>27</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6014,45 +6014,45 @@
         <v>53.8</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>35.9</v>
+        <v>44.9</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>41.2</v>
+        <v>51.6</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>47.1</v>
+        <v>58.1</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6072,25 +6072,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>73.2</v>
+        <v>60.2</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>36.6</v>
+        <v>42.2</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6099,21 +6099,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>70</v>
+        <v>62.2</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>45</v>
+        <v>56.8</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -6266,14 +6266,14 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>44.4</v>
+        <v>38.2</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -6282,21 +6282,21 @@
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6316,25 +6316,25 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>54.8</v>
+        <v>47.2</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>43.8</v>
+        <v>39.3</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="K96" s="3" t="n">
-        <v>61.9</v>
+        <v>55.6</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N96" s="3" t="n">
-        <v>42.9</v>
+        <v>37</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6499,25 +6499,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>62.9</v>
+        <v>52.1</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>42.3</v>
+        <v>44.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6526,21 +6526,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>70</v>
+        <v>46.6</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>64</v>
+        <v>52.2</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6571,14 +6571,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>44.2</v>
+        <v>46.3</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6587,21 +6587,21 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>66.7</v>
+        <v>48.1</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>50</v>
+        <v>59.3</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6621,25 +6621,25 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>61.8</v>
+        <v>46.5</v>
       </c>
       <c r="E101" s="4" t="n">
         <v>144</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>45.8</v>
+        <v>47.9</v>
       </c>
       <c r="H101" s="4" t="n">
         <v>144</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="K101" s="3" t="n">
-        <v>61.5</v>
+        <v>41.4</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="N101" s="3" t="n">
-        <v>42.3</v>
+        <v>47.1</v>
       </c>
       <c r="O101" s="4" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6682,25 +6682,25 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>79.7</v>
+        <v>59.5</v>
       </c>
       <c r="E102" s="4" t="n">
         <v>79</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>39.2</v>
+        <v>38</v>
       </c>
       <c r="H102" s="4" t="n">
         <v>79</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6754,14 +6754,14 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>43.7</v>
+        <v>38.2</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>38.2</v>
+        <v>50</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6804,25 +6804,25 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>53.2</v>
+        <v>48.2</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>46.8</v>
+        <v>43.2</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>62</v>
+        <v>55.9</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>40</v>
+        <v>44.1</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7101,48 +7101,48 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-U</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>42.9</v>
-      </c>
       <c r="N2" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
         <v>50</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7257,20 +7257,20 @@
         <v>50</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>3</v>
@@ -7305,19 +7305,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>44.4</v>
+        <v>80</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7325,37 +7325,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -7589,57 +7589,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-N</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-D</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P9" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7811,44 +7811,48 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr"/>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -7869,46 +7873,46 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>85.7</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>85.7</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -7916,10 +7920,10 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8020,48 +8024,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>53.3</v>
+        <v>57.1</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>53.3</v>
+        <v>38.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -8082,34 +8086,34 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>60</v>
+        <v>51.9</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>50</v>
+        <v>59.3</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8118,21 +8122,21 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>62.5</v>
+        <v>47.1</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>62.5</v>
+        <v>52.9</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -8224,7 +8228,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8233,25 +8237,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>42.1</v>
+        <v>45.8</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8260,21 +8264,21 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -8295,19 +8299,19 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>75</v>
+        <v>54.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8315,37 +8319,37 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-U</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>83.3</v>
-      </c>
       <c r="N19" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -8437,7 +8441,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -8446,48 +8450,48 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>57.7</v>
+        <v>51.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>75</v>
+        <v>63.6</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>66.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -8650,7 +8654,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8659,48 +8663,48 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-U</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J24" s="4" t="n">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q24" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -9285,57 +9289,57 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>58.3</v>
+        <v>72.7</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -9427,34 +9431,34 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>100</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
         <v>100</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9703,19 +9707,19 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>43.3</v>
+        <v>46.9</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -9723,14 +9727,14 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -9739,21 +9743,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -10263,57 +10267,57 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>66.7</v>
+        <v>42.9</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -10334,7 +10338,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10343,48 +10347,48 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>55.6</v>
+        <v>83.3</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -10405,7 +10409,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10414,10 +10418,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -10428,23 +10432,23 @@
         <v>50</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -10452,10 +10456,10 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -10752,34 +10756,34 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>75</v>
+        <v>36.1</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>41.7</v>
+        <v>61.1</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -10788,21 +10792,21 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -10894,7 +10898,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10903,10 +10907,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -10914,14 +10918,14 @@
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>63.6</v>
+        <v>75</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -10930,10 +10934,10 @@
         </is>
       </c>
       <c r="M56" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -10941,10 +10945,10 @@
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -10965,7 +10969,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10974,25 +10978,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>69.2</v>
+        <v>54.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -11004,18 +11008,18 @@
         <v>66.7</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -11036,39 +11040,39 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-D</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>N-U-U-N</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
@@ -11249,19 +11253,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -11269,37 +11273,37 @@
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M61" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P61" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -11462,7 +11466,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -11471,10 +11475,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>38.1</v>
+        <v>40.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -11482,26 +11486,26 @@
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.4</v>
+        <v>42.3</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -11509,10 +11513,10 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -11604,57 +11608,57 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>44.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-N</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M66" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P66" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -11675,7 +11679,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -11687,7 +11691,7 @@
         <v>100</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -11698,11 +11702,11 @@
         <v>100</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -11746,7 +11750,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11755,25 +11759,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11782,21 +11786,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -12101,7 +12105,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12110,30 +12114,30 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M73" s="3" t="n">
@@ -12172,7 +12176,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -12181,10 +12185,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12192,14 +12196,14 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>53.8</v>
+        <v>48.1</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -12208,10 +12212,10 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -12219,10 +12223,10 @@
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
@@ -12243,7 +12247,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -12252,30 +12256,30 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M75" s="3" t="n">
@@ -12314,7 +12318,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -12323,25 +12327,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>47.6</v>
+        <v>55.2</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -12350,21 +12354,21 @@
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
@@ -12882,7 +12886,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12891,25 +12895,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>50</v>
+        <v>57.9</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -12918,10 +12922,10 @@
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -12932,7 +12936,7 @@
         <v>50</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -13379,7 +13383,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -13388,48 +13392,48 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G91" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>57.1</v>
-      </c>
       <c r="N91" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -13450,7 +13454,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13459,25 +13463,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13486,21 +13490,21 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -13663,7 +13667,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -13672,25 +13676,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>85.7</v>
+        <v>81.8</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -13699,21 +13703,21 @@
         </is>
       </c>
       <c r="M95" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P95" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -13734,19 +13738,19 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>57.1</v>
+        <v>42.4</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -13754,37 +13758,37 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>57.1</v>
+        <v>45.5</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M96" s="3" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P96" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
@@ -13947,57 +13951,57 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>53.3</v>
+        <v>46.4</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M99" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="N99" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P99" s="3" t="n">
-        <v>50</v>
+        <v>63.6</v>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
@@ -14018,57 +14022,57 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>52.9</v>
+        <v>38.9</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -14089,19 +14093,19 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>37.5</v>
+        <v>34.8</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -14109,37 +14113,37 @@
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="N101" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P101" s="3" t="n">
-        <v>60</v>
+        <v>44.4</v>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -14160,7 +14164,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14169,10 +14173,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14180,37 +14184,37 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>36.8</v>
+        <v>52.9</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -14231,7 +14235,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14240,10 +14244,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -14251,37 +14255,37 @@
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>52.4</v>
+        <v>46.2</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M103" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N103" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P103" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -14302,16 +14306,16 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G104" s="4" t="n">
         <v>25</v>
@@ -14322,37 +14326,37 @@
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M104" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36.5</v>
+        <v>40.8</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>78.3</v>
+        <v>56</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>39.1</v>
+        <v>44</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -726,7 +726,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>63</v>
+        <v>59.7</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45.1</v>
+        <v>46.8</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>44.8</v>
+        <v>48.4</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61.3</v>
+        <v>53.6</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -902,14 +902,14 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>48</v>
+        <v>42.5</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>61.3</v>
+        <v>46.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>51.6</v>
+        <v>40.8</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -952,48 +952,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-N</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-D</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N8" s="3" t="n">
-        <v>56.2</v>
+        <v>100</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.6</v>
+        <v>54.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.4</v>
+        <v>43.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>59.3</v>
+        <v>51.4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1085,14 +1085,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>47.6</v>
+        <v>52</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43.8</v>
+        <v>42</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>57.4</v>
+        <v>63</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>45.9</v>
+        <v>54.3</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1562,25 +1562,25 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>68.8</v>
+        <v>59.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>42.5</v>
+        <v>46.3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>41.4</v>
+        <v>47.8</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>62.9</v>
+        <v>46.6</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>42.9</v>
+        <v>45.6</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>66.7</v>
+        <v>45.8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.4</v>
+        <v>47.9</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>66.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>50.6</v>
+        <v>42.6</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1939,14 +1939,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>41.7</v>
+        <v>37.5</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>50.6</v>
+        <v>66.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -2000,37 +2000,37 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>45</v>
+        <v>55.6</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>44.6</v>
+        <v>44.2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2244,14 +2244,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68</v>
+        <v>76.7</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>56</v>
+        <v>61.7</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>50</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>50</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>66.7</v>
+        <v>85</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,30 +2599,30 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>47.1</v>
+        <v>75</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,48 +2660,48 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>53.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
         <v>46.2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>46.5</v>
+        <v>59.4</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,14 +2854,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>52.1</v>
+        <v>40</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>40</v>
+        <v>59.5</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -3200,57 +3200,57 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>42.4</v>
+        <v>62.5</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>50.8</v>
+        <v>46.9</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>42.9</v>
+        <v>46.7</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3270,48 +3270,48 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>64.2</v>
+        <v>56.4</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
       <c r="N46" s="3" t="n">
-        <v>40</v>
+        <v>43.5</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>58.8</v>
+        <v>81.8</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>40</v>
+        <v>43.2</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>52.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>42.5</v>
+        <v>47.4</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3403,14 +3403,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46.7</v>
+        <v>42</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>41.2</v>
+        <v>60</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3453,25 +3453,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>56.1</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>37.8</v>
+        <v>43.9</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3480,21 +3480,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>66.7</v>
+        <v>56.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>41.7</v>
+        <v>43.8</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>57.9</v>
+        <v>57.6</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45.3</v>
+        <v>45.6</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>56.2</v>
+        <v>58.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3708,14 +3708,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>56.2</v>
+        <v>44.4</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3727,18 +3727,18 @@
         <v>50</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>52.5</v>
+        <v>51.2</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>160</v>
@@ -3830,14 +3830,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>160</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>48.4</v>
+        <v>51.7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>45.2</v>
+        <v>51.7</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>57.6</v>
+        <v>57.1</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3952,14 +3952,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>48.8</v>
+        <v>42.3</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>55.6</v>
+        <v>58</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4002,25 +4002,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>64.3</v>
+        <v>43.8</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4029,21 +4029,21 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>40.5</v>
+        <v>45.3</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>72</v>
+        <v>68.3</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>44</v>
+        <v>42.9</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4124,25 +4124,25 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>62</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>41.8</v>
+        <v>42.9</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>61.1</v>
+        <v>70</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>38.9</v>
+        <v>40</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4185,25 +4185,25 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>62.5</v>
+        <v>48.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>75</v>
+        <v>55.6</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>57.3</v>
+        <v>73.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>48</v>
+        <v>46.7</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>54.2</v>
+        <v>76.2</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>42.4</v>
+        <v>42.9</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4734,48 +4734,48 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>58.1</v>
+        <v>66</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-U</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G70" s="3" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="N70" s="3" t="n">
-        <v>41.9</v>
+        <v>42.6</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4917,25 +4917,25 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>44.4</v>
+        <v>41</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>66.7</v>
+        <v>65.2</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N73" s="3" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5100,25 +5100,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>62.8</v>
+        <v>61</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>41.9</v>
+        <v>44.2</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5164,22 +5164,22 @@
         <v>66.7</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>47.9</v>
+        <v>39.5</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5188,21 +5188,21 @@
         </is>
       </c>
       <c r="K77" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>35.7</v>
+        <v>45.8</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5222,25 +5222,25 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>59</v>
+        <v>56.8</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>51.3</v>
+        <v>59.5</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -5249,21 +5249,21 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>64.3</v>
+        <v>63.6</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N78" s="3" t="n">
-        <v>64.3</v>
+        <v>63.6</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>62.8</v>
+        <v>59</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>55.6</v>
+        <v>63.2</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>61.1</v>
+        <v>47.4</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -5335,57 +5335,57 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>53.3</v>
+        <v>46.8</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G80" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="N80" s="3" t="n">
-        <v>43.8</v>
+        <v>44.8</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>55.1</v>
+        <v>50.9</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5416,37 +5416,37 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>42.9</v>
+        <v>47.4</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,48 +5466,48 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>73</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>43.2</v>
+        <v>57.7</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>76.5</v>
+        <v>50</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>52.9</v>
+        <v>60</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>67.7</v>
+        <v>70.5</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5599,14 +5599,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40.3</v>
+        <v>44.3</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>50</v>
+        <v>76.2</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>44.8</v>
+        <v>46.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>40.7</v>
+        <v>43.5</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>58.2</v>
+        <v>63.5</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>41.8</v>
+        <v>43.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>66.7</v>
+        <v>63.1</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="E88" s="4" t="n">
         <v>185</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>50.3</v>
+        <v>67.2</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,14 +5904,14 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>43.1</v>
+        <v>49.3</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>47</v>
+        <v>58.3</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>38.6</v>
+        <v>52.8</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>55.3</v>
+        <v>63.9</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>217</v>
+        <v>72</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5965,14 +5965,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>44.2</v>
+        <v>58.3</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>217</v>
+        <v>72</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>55.8</v>
+        <v>58.8</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>43.2</v>
+        <v>58.8</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6076,25 +6076,25 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -6103,21 +6103,21 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>66.7</v>
+        <v>51.5</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>46.7</v>
+        <v>51.5</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,37 +6137,37 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>58.6</v>
+        <v>63.4</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>44.8</v>
+        <v>41.5</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>77.8</v>
+        <v>85.7</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>73.5</v>
+        <v>58</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6392,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>42.9</v>
+        <v>40.6</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>84.2</v>
+        <v>63.3</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>47.4</v>
+        <v>40</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>55.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6575,14 +6575,14 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>37.1</v>
+        <v>40.4</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="K100" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>37.5</v>
+        <v>46.7</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6697,14 +6697,14 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>35.8</v>
+        <v>41.7</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="K102" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N102" s="3" t="n">
-        <v>35.5</v>
+        <v>52.4</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6747,25 +6747,25 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>85.5</v>
+        <v>75</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -6774,21 +6774,21 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>82</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N103" s="3" t="n">
-        <v>36</v>
+        <v>40.7</v>
       </c>
       <c r="O103" s="4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>58.8</v>
+        <v>60.9</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -6819,26 +6819,26 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>41.2</v>
+        <v>40.2</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K104" s="3" t="n">
-        <v>46.7</v>
+        <v>71</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="N104" s="3" t="n">
-        <v>46.7</v>
+        <v>45.2</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6869,25 +6869,25 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>53.9</v>
+        <v>74.3</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>40.8</v>
+        <v>40</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -6896,21 +6896,21 @@
         </is>
       </c>
       <c r="K105" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="L105" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="n">
-        <v>42.9</v>
-      </c>
       <c r="O105" s="4" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -7105,48 +7105,48 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -7265,30 +7265,26 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7380,7 +7376,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7389,10 +7385,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7400,14 +7396,14 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46.7</v>
+        <v>66.7</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7416,21 +7412,21 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -7451,57 +7447,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-N</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="n">
-        <v>57.1</v>
+        <v>35.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -7522,7 +7518,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7531,48 +7527,44 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>66.7</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7620,30 +7612,30 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -7691,7 +7683,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7700,21 +7692,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -7735,7 +7727,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7744,10 +7736,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>61.1</v>
+        <v>66.7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7755,14 +7747,14 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>47.2</v>
+        <v>43.6</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7771,21 +7763,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>53.3</v>
+        <v>45</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -8232,19 +8224,19 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -8252,14 +8244,14 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>45</v>
+        <v>62.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -8271,7 +8263,7 @@
         <v>80</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -8279,10 +8271,10 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -8303,19 +8295,19 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>81.8</v>
+        <v>42.1</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -8323,26 +8315,26 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>36.4</v>
+        <v>47.4</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -8353,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -8374,7 +8366,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8383,25 +8375,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>61.5</v>
+        <v>81.8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>38.5</v>
+        <v>45.5</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8410,21 +8402,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -8658,7 +8650,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -8667,10 +8659,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>57.1</v>
+        <v>76.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -8678,14 +8670,14 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>57.1</v>
+        <v>47.6</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -8694,21 +8686,21 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>100</v>
+        <v>61.5</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -8729,19 +8721,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -8749,37 +8741,37 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>47.8</v>
+        <v>80</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -9036,7 +9028,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -9045,10 +9037,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -9056,10 +9048,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -9222,7 +9214,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -9231,25 +9223,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>87.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>62.5</v>
+        <v>45.5</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -9258,21 +9250,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -9435,7 +9427,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9444,10 +9436,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -9458,34 +9450,30 @@
         <v>100</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-N</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>100</v>
-      </c>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9506,7 +9494,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9515,25 +9503,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>56.2</v>
-      </c>
       <c r="J36" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -9542,21 +9530,21 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9719,7 +9707,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9728,10 +9716,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>47.4</v>
+        <v>60.7</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -9739,26 +9727,26 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>47.4</v>
+        <v>60.7</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>60</v>
+        <v>61.5</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -9766,10 +9754,10 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>80</v>
+        <v>69.2</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -10137,19 +10125,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -10157,37 +10145,37 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q45" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -10208,7 +10196,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10217,25 +10205,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>52.6</v>
+        <v>44.8</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -10244,21 +10232,21 @@
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -10279,7 +10267,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10288,48 +10276,48 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>59.1</v>
+        <v>81.8</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>40.9</v>
+        <v>36.4</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -10350,7 +10338,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10359,25 +10347,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>58.3</v>
+        <v>54.5</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10386,21 +10374,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -10421,19 +10409,19 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -10441,23 +10429,23 @@
         </is>
       </c>
       <c r="I49" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-D</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>100</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>2</v>
@@ -10701,7 +10689,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -10710,48 +10698,48 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="P53" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="Q53" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-N</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q53" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -10843,7 +10831,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -10852,10 +10840,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -10863,14 +10851,14 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>57.1</v>
+        <v>40.6</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -10879,10 +10867,10 @@
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>55.6</v>
+        <v>46.2</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -10890,10 +10878,10 @@
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>55.6</v>
+        <v>46.2</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -10985,7 +10973,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10994,10 +10982,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>59.5</v>
+        <v>47.1</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -11005,26 +10993,26 @@
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -11032,10 +11020,10 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -11056,39 +11044,39 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
@@ -11099,7 +11087,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
@@ -11127,7 +11115,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -11136,10 +11124,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -11147,14 +11135,14 @@
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -11166,18 +11154,18 @@
         <v>80</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P59" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -11198,7 +11186,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -11207,48 +11195,48 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>72.2</v>
+        <v>63.6</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>44.4</v>
+        <v>45.5</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M60" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P60" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -11269,7 +11257,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -11278,44 +11266,48 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J61" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>D-N-U-U</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="N61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="n">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="Q61" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-N</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -11336,7 +11328,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -11345,10 +11337,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46.9</v>
+        <v>100</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11356,14 +11348,14 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>53.1</v>
+        <v>66.7</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -11372,21 +11364,21 @@
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P62" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -11900,7 +11892,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11909,10 +11901,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>61.5</v>
+        <v>63.3</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -11920,14 +11912,14 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -11936,10 +11928,10 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11939,10 @@
         </is>
       </c>
       <c r="P70" s="3" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -12113,7 +12105,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12122,10 +12114,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -12133,14 +12125,14 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -12149,10 +12141,10 @@
         </is>
       </c>
       <c r="M73" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -12160,10 +12152,10 @@
         </is>
       </c>
       <c r="P73" s="3" t="n">
-        <v>75</v>
+        <v>58.3</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -12326,57 +12318,57 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-U</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-N</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M76" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -12397,7 +12389,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -12406,25 +12398,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>69.2</v>
+        <v>61.5</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -12433,21 +12425,21 @@
         </is>
       </c>
       <c r="M77" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P77" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -12468,7 +12460,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -12477,10 +12469,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>58.3</v>
+        <v>57.1</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -12488,37 +12480,37 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>U-N-N-D</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J78" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>U-N-N-U</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="n">
-        <v>66.7</v>
-      </c>
       <c r="N78" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P78" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -12539,7 +12531,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -12548,25 +12540,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>63.6</v>
+        <v>60.9</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -12578,18 +12570,18 @@
         <v>100</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P79" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -12610,7 +12602,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -12619,48 +12611,48 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>64.7</v>
+        <v>48.7</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I80" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-N</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P80" s="3" t="n">
-        <v>57.1</v>
+        <v>54.5</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -12681,7 +12673,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12690,10 +12682,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -12701,14 +12693,14 @@
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -12717,21 +12709,21 @@
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -12752,7 +12744,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12761,25 +12753,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -12791,18 +12783,18 @@
         <v>100</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -12894,57 +12886,57 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>57.1</v>
+        <v>80</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>42.9</v>
+        <v>53.3</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -13056,7 +13048,7 @@
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>55.3</v>
+        <v>57.9</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>38</v>
@@ -13107,7 +13099,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -13116,25 +13108,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>64.3</v>
+        <v>57.6</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -13143,21 +13135,21 @@
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>66.7</v>
+        <v>43.8</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
@@ -13249,7 +13241,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -13258,48 +13250,48 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>57.9</v>
+        <v>69.2</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>49.1</v>
+        <v>38.5</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>56.5</v>
+        <v>60</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>39.1</v>
+        <v>60</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -13320,7 +13312,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -13329,10 +13321,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>61.3</v>
+        <v>55.6</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13340,14 +13332,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>40.3</v>
+        <v>44.4</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13356,21 +13348,21 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>70.8</v>
+        <v>100</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -13462,7 +13454,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -13471,10 +13463,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>85.7</v>
+        <v>86.7</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13482,14 +13474,14 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -13498,21 +13490,21 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N92" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q92" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -13533,7 +13525,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -13542,37 +13534,37 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>53.3</v>
+        <v>75</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M93" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N93" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -13583,7 +13575,7 @@
         <v>50</v>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -13813,7 +13805,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -13822,25 +13814,25 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>80</v>
+        <v>64.3</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>60</v>
+        <v>35.7</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -13849,21 +13841,21 @@
         </is>
       </c>
       <c r="M97" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N97" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P97" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -14026,7 +14018,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -14035,25 +14027,25 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>47.8</v>
+        <v>62.5</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>43.5</v>
+        <v>37.5</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -14062,21 +14054,21 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>57.1</v>
+        <v>75</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P100" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -14168,7 +14160,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -14177,25 +14169,25 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>41.2</v>
+        <v>44.4</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -14204,14 +14196,14 @@
         </is>
       </c>
       <c r="M102" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N102" s="4" t="n">
         <v>6</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P102" s="3" t="n">
@@ -14239,7 +14231,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -14248,48 +14240,48 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>U-U-N-U</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I103" s="3" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J103" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>U-U-N-N</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P103" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
@@ -14310,19 +14302,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>54.5</v>
+        <v>84</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14330,37 +14322,37 @@
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>72.7</v>
+        <v>40</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M104" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P104" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -14381,19 +14373,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -14404,34 +14396,34 @@
         <v>50</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M105" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N105" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P105" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BVR_istatistik_tahminleri.xlsx
+++ b/BVR_istatistik_tahminleri.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>56.6</v>
+        <v>53.9</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>43.4</v>
+        <v>44.1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,21 +674,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>56.2</v>
+        <v>52.3</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>46.9</v>
+        <v>46.2</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>38.6</v>
+        <v>41.4</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -735,21 +735,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>60</v>
+        <v>47.8</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>42.5</v>
+        <v>48.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>71.8</v>
+        <v>60.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>48.7</v>
+        <v>52.2</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -821,7 +821,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>46.8</v>
+        <v>52.3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,21 +857,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>64.5</v>
+        <v>52.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>48.4</v>
+        <v>43.5</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -943,19 +943,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>60</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -963,37 +963,37 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>60</v>
+        <v>54.3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1196,25 +1196,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>58.5</v>
+        <v>52.9</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>44.6</v>
+        <v>44.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1223,21 +1223,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>55.6</v>
+        <v>51.7</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>48.1</v>
+        <v>55.2</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1257,25 +1257,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>65.5</v>
+        <v>51.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1623,37 +1623,37 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45.6</v>
+        <v>50</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>45.8</v>
+        <v>55.6</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>47.9</v>
+        <v>55.6</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1695,14 +1695,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>42.6</v>
+        <v>50.6</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>73.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -2102,57 +2102,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>47.1</v>
+        <v>80</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>84</v>
+        <v>63.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2427,14 +2427,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>85</v>
+        <v>55.6</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2610,14 +2610,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>75</v>
+        <v>56.5</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-N</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2660,48 +2660,48 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46.2</v>
+        <v>44.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2782,25 +2782,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2809,21 +2809,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>54.5</v>
+        <v>62.5</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>36.4</v>
+        <v>43.8</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>59.4</v>
+        <v>46.5</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2854,37 +2854,37 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-N</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>155</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>59.5</v>
-      </c>
       <c r="L39" s="4" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2965,37 +2965,37 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>55.2</v>
+        <v>58.9</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>58.6</v>
+        <v>43.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>64.3</v>
+        <v>43.8</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
@@ -3139,34 +3139,34 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>40</v>
+        <v>61.5</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3178,18 +3178,18 @@
         <v>100</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3525,14 +3525,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>47.3</v>
+        <v>39.7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3541,21 +3541,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>72.7</v>
+        <v>83.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>54.5</v>
+        <v>55.6</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-U-N</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3575,25 +3575,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-N</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4063,25 +4063,25 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>63.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>45.3</v>
+        <v>40.5</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>68.3</v>
+        <v>72</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>42.9</v>
+        <v>44</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>73.3</v>
+        <v>57.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46.7</v>
+        <v>48</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>76.2</v>
+        <v>54.2</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>63.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4318,14 +4318,14 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>47.4</v>
+        <v>57.1</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -4334,21 +4334,21 @@
         </is>
       </c>
       <c r="K63" s="3" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N63" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4368,48 +4368,48 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>57.6</v>
+        <v>55.6</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>40.7</v>
+        <v>50.8</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-D</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K64" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N64" s="3" t="n">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -4542,57 +4542,57 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>52.6</v>
+        <v>38.5</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4673,48 +4673,48 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>51.1</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>44.4</v>
+        <v>64.3</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>44.4</v>
+        <v>75</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4795,25 +4795,25 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>52.9</v>
+        <v>55.2</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>40</v>
+        <v>46.5</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
@@ -4847,19 +4847,19 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>53.8</v>
+        <v>45.8</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4867,37 +4867,37 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5039,48 +5039,48 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>53.3</v>
+        <v>55.6</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>46.7</v>
+        <v>37</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>54.5</v>
+        <v>42.9</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5283,25 +5283,25 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>59</v>
+        <v>62.8</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>63.2</v>
+        <v>55.6</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N79" s="3" t="n">
-        <v>47.4</v>
+        <v>61.1</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5466,48 +5466,48 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>57.7</v>
+        <v>43.2</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>50</v>
+        <v>76.5</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>60</v>
+        <v>52.9</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>70.5</v>
+        <v>67.7</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5599,14 +5599,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>44.3</v>
+        <v>40.3</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>76.2</v>
+        <v>50</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5649,10 +5649,10 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>47.8</v>
+        <v>60.9</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -5660,37 +5660,37 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>47.8</v>
+        <v>49.2</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K85" s="3" t="n">
-        <v>36.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N85" s="3" t="n">
-        <v>47.4</v>
+        <v>46.7</v>
       </c>
       <c r="O85" s="4" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5771,25 +5771,25 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>63.5</v>
+        <v>58.2</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>43.6</v>
+        <v>41.8</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5798,21 +5798,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>63.1</v>
+        <v>66.7</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>67.2</v>
+        <v>57.2</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>187</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-D</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="L89" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="n">
         <v>49.3</v>
       </c>
-      <c r="H89" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="n">
-        <v>52.8</v>
-      </c>
       <c r="O89" s="4" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>49.2</v>
+        <v>41.2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -6026,14 +6026,14 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>44.6</v>
+        <v>47.3</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="K91" s="3" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="N91" s="3" t="n">
-        <v>53.8</v>
+        <v>46.7</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>63.4</v>
+        <v>67.7</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -6151,11 +6151,11 @@
         <v>41.5</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-D</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -6164,21 +6164,21 @@
         </is>
       </c>
       <c r="K93" s="3" t="n">
-        <v>85.7</v>
+        <v>63.6</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N93" s="3" t="n">
-        <v>42.9</v>
+        <v>63.6</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6259,48 +6259,48 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>72.7</v>
+        <v>70.7</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>40.9</v>
+        <v>41.5</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K95" s="3" t="n">
-        <v>50</v>
+        <v>91.7</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N95" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>58</v>
+        <v>73.5</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6392,14 +6392,14 @@
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>40.6</v>
+        <v>42.9</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>D-N-U-N</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6408,21 +6408,21 @@
         </is>
       </c>
       <c r="K97" s="3" t="n">
-        <v>63.3</v>
+        <v>84.2</v>
       </c>
       <c r="L97" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N97" s="3" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="O97" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>68